--- a/Assets/Tools/Luban/Datas/content_visual.xlsx
+++ b/Assets/Tools/Luban/Datas/content_visual.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -520,6 +520,16 @@
           <t>玩家化身</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>visual.face.avatar.default</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>visual.icon.avatar.default</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -537,6 +547,16 @@
           <t>[使用时] 将目标怪物卡护甲降低10点</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>visual.face.help.armor_breaking_hammer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>visual.icon.help.armor_breaking_hammer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -554,6 +574,16 @@
           <t>[场上] 当正交相邻格补牌为怪物卡时，对其造成10点伤害，之后移除本卡</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>visual.face.help.bear_trap</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>visual.icon.help.bear_trap</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -571,6 +601,16 @@
           <t>[使用时] 扣除5点血量上限并随机获得攻击+1、护甲+1、50金币或随机遗物</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>visual.face.help.blood_conversion</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>visual.icon.help.blood_conversion</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -588,6 +628,16 @@
           <t>[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>visual.face.help.blue_chest_card</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>visual.icon.help.blue_chest_card</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -605,6 +655,16 @@
           <t>[使用时] 对所有怪物卡造成4点伤害</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>visual.face.help.bomb</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>visual.icon.help.bomb</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -622,6 +682,16 @@
           <t>[使用时] 玩家下一次对怪物造成的战斗伤害翻倍</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>visual.face.help.brutality_card</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>visual.icon.help.brutality_card</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -639,6 +709,16 @@
           <t>[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>visual.face.help.common_chest_card</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>visual.icon.help.common_chest_card</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -656,6 +736,16 @@
           <t>[场上] 处于格1时，对怪物卡使用的帮助卡触发两次；[道具牌格] 对玩家卡使用的帮助卡生效两次，触发后永久移除本卡</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>visual.face.help.doubling_tower</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>visual.icon.help.doubling_tower</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -673,6 +763,16 @@
           <t>[使用时] 对目标怪物卡造成等同于玩家攻击的伤害</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>visual.face.help.fireball</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>visual.icon.help.fireball</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -690,6 +790,16 @@
           <t>[使用时] 对玩家造成4点伤害并永久移除本卡</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>visual.face.help.flame</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>visual.icon.help.flame</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -707,6 +817,16 @@
           <t>[使用时] 将玩家卡血量回满</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>visual.face.help.food_card</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>visual.icon.help.food_card</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -724,6 +844,16 @@
           <t>[使用时] 为玩家提供50金币</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>visual.face.help.gold_card</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>visual.icon.help.gold_card</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -741,6 +871,16 @@
           <t>[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>visual.face.help.golden_chest_card</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>visual.icon.help.golden_chest_card</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -758,6 +898,16 @@
           <t>[使用时] 恢复10点血量</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>visual.face.help.healing_potion</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>visual.icon.help.healing_potion</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -775,6 +925,16 @@
           <t>[场上] 移动到玩家卡正交相邻格时，为玩家恢复2点血量；[道具牌格] 玩家与怪物战斗时，恢复1点血量；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>visual.face.help.healing_spring</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>visual.icon.help.healing_spring</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -792,6 +952,16 @@
           <t>[使用时] 对目标怪物卡造成等同于玩家当前血量的伤害</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>visual.face.help.impact_tutorial</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>visual.icon.help.impact_tutorial</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -809,6 +979,16 @@
           <t>[使用时] 移除一张非精英非层主怪物卡，并获得等同于其当前护甲的护甲</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>visual.face.help.kidnapping</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>visual.icon.help.kidnapping</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -826,6 +1006,16 @@
           <t>[场上] 移动到格3时，若格6为非精英非层主怪物，则移除该怪物和本卡；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>visual.face.help.rolling_stone</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>visual.icon.help.rolling_stone</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -843,6 +1033,16 @@
           <t>[使用时] 逆时针旋转一次</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>visual.face.help.rotation_wheel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>visual.icon.help.rotation_wheel</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -860,6 +1060,16 @@
           <t>[使用时] 对目标怪物卡造成等同于玩家当前护甲的伤害</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>visual.face.help.shield_bash_tutorial</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>visual.icon.help.shield_bash_tutorial</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -877,6 +1087,16 @@
           <t>[使用时] 选择攻击+1、护甲+1或血量上限与当前血量+2</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>visual.face.help.stat_boost_card</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>visual.icon.help.stat_boost_card</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -894,6 +1114,16 @@
           <t>[使用时] 玩家获得5点护甲</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>visual.face.help.sturdy_shield</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>visual.icon.help.sturdy_shield</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
@@ -911,6 +1141,16 @@
           <t>[使用时] 选择除玩家卡外的两张卡牌互换所在格子位置</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>visual.face.help.swap_card</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>visual.icon.help.swap_card</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -928,6 +1168,16 @@
           <t>[使用时] 选择除玩家卡外的一张卡牌洗回战斗卡组</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>visual.face.help.teleport_card</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>visual.icon.help.teleport_card</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -945,6 +1195,16 @@
           <t>[使用时] 对目标怪物卡造成6点伤害</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>visual.face.help.throwing_knife</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>visual.icon.help.throwing_knife</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -962,6 +1222,16 @@
           <t>[使用时] 下一次玩家受到伤害时，该次伤害变为0</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>visual.face.help.ward_magic_card</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>visual.icon.help.ward_magic_card</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -979,6 +1249,16 @@
           <t>[场上] 移动到角格时，对随机怪物造成3点伤害；触发4次后移除本卡；[道具牌格] 玩家与怪物战斗时，对随机一张怪物卡造成2点伤害；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>visual.face.help.watchtower</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>visual.icon.help.watchtower</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -998,7 +1278,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.beggar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.beggar</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1305,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.big_orc</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.big_orc</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1332,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.big_skeleton</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.big_skeleton</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1359,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.big_stone</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.big_stone</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1381,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.bone_club_skeleton</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.bone_club_skeleton</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1408,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.bone_courier</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.bone_courier</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1435,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.brainless_orc</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.brainless_orc</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1462,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.dragon_cult_leader</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.dragon_cult_leader</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1489,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.dragon_follower</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.dragon_follower</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1516,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.executioner</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.executioner</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1543,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.fire_bather</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_bather</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1570,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.fire_cult_leader</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_cult_leader</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1597,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.fire_dragon</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_dragon</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1624,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.fire_priest</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_priest</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1651,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.fire_swallower</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_swallower</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1678,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.friendly_ancient</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.friendly_ancient</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1705,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.giant_skeleton</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.giant_skeleton</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1732,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.growing_stone</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.growing_stone</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1759,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.headless_skeleton</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.headless_skeleton</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1786,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.hoodlum</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.hoodlum</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1813,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.killer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.killer</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1840,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.megalith</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.megalith</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1867,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.mist</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.mist</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1894,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.multi_bone_worm</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.multi_bone_worm</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1921,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.observer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.observer</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1948,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.old_orc</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.old_orc</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1975,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.orc_boss</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_boss</t>
         </is>
       </c>
     </row>
@@ -1587,7 +2002,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.orc_commander</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_commander</t>
         </is>
       </c>
     </row>
@@ -1609,7 +2029,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.orc_quartermaster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_quartermaster</t>
         </is>
       </c>
     </row>
@@ -1631,7 +2056,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.orc_warrior</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_warrior</t>
         </is>
       </c>
     </row>
@@ -1653,7 +2083,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.pickpocket</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.pickpocket</t>
         </is>
       </c>
     </row>
@@ -1675,7 +2110,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.ringleader</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.ringleader</t>
         </is>
       </c>
     </row>
@@ -1697,7 +2137,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.rogue</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.rogue</t>
         </is>
       </c>
     </row>
@@ -1719,7 +2164,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.rolling_stone_man</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.rolling_stone_man</t>
         </is>
       </c>
     </row>
@@ -1741,7 +2191,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.rotating_cub</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.rotating_cub</t>
         </is>
       </c>
     </row>
@@ -1763,7 +2218,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.salamander</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.salamander</t>
         </is>
       </c>
     </row>
@@ -1785,7 +2245,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.sharp_stone</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.sharp_stone</t>
         </is>
       </c>
     </row>
@@ -1807,7 +2272,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.shelter_stone</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.shelter_stone</t>
         </is>
       </c>
     </row>
@@ -1829,7 +2299,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.skeleton_king</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skeleton_king</t>
         </is>
       </c>
     </row>
@@ -1851,7 +2326,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.skeleton_mage</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skeleton_mage</t>
         </is>
       </c>
     </row>
@@ -1873,7 +2353,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.skeleton_taunter</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skeleton_taunter</t>
         </is>
       </c>
     </row>
@@ -1895,7 +2380,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>deck.skeleton_legion</t>
+          <t>visual.face.monster.skull_head</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skull_head</t>
         </is>
       </c>
     </row>
@@ -1917,7 +2407,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.sky_eye</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.sky_eye</t>
         </is>
       </c>
     </row>
@@ -1939,7 +2434,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.smart_orc</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.smart_orc</t>
         </is>
       </c>
     </row>
@@ -1961,7 +2461,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.smuggler</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.smuggler</t>
         </is>
       </c>
     </row>
@@ -1983,7 +2488,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.space_master</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.space_master</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2515,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.stepwalker</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stepwalker</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2537,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>deck.dragon</t>
+          <t>visual.face.monster.stone_golem</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_golem</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2559,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.stone_man</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_man</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2586,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.stone_shrimp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_shrimp</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2613,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.stone_swallower</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_swallower</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2640,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>deck.stone_legion</t>
+          <t>visual.face.monster.stone_thrower</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_thrower</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2667,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.thug</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.thug</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2689,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.vagrant</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.vagrant</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2711,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.veteran_orc</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.veteran_orc</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2738,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.void_cub</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.void_cub</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2760,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.void_lost</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.void_lost</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2787,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>deck.wandering_legion</t>
+          <t>visual.face.monster.wandering_child</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.wandering_child</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2814,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>deck.void</t>
+          <t>visual.face.monster.world_turning_hand</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.world_turning_hand</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2841,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>deck.orc_legion</t>
+          <t>visual.face.monster.young_orc</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.young_orc</t>
         </is>
       </c>
     </row>
@@ -2288,10 +2868,9 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>visual.face.deck.dragon</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_42</t>
@@ -2314,6 +2893,11 @@
           <t>兽人军团牌组</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>visual.face.deck.orc_legion</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
@@ -2331,6 +2915,11 @@
           <t>骷髅军团牌组</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>visual.face.deck.skeleton_legion</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
@@ -2348,6 +2937,11 @@
           <t>石人军团牌组</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>visual.face.deck.stone_legion</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
@@ -2365,6 +2959,11 @@
           <t>虚空牌组</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>visual.face.deck.void</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
@@ -2382,6 +2981,11 @@
           <t>流浪军团牌组</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>visual.face.deck.wandering_legion</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
@@ -2399,6 +3003,16 @@
           <t>所有恢复血量效果翻倍</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>visual.face.relic.craving</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.craving</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
@@ -2416,6 +3030,16 @@
           <t>所有怪物攻击-1</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>visual.face.relic.dragon_scale_armor</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.dragon_scale_armor</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
@@ -2433,6 +3057,16 @@
           <t>金币抵消护甲伤害</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>visual.face.relic.gold_armor</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.gold_armor</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
@@ -2450,6 +3084,16 @@
           <t>击杀怪物时获得2金币</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>visual.face.relic.gold_knife</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.gold_knife</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
@@ -2467,6 +3111,16 @@
           <t>基础护甲+1，按基础护甲补当前护甲</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>visual.face.relic.heavy_armor</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.heavy_armor</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
@@ -2484,6 +3138,16 @@
           <t>使用帮助卡时获得护甲</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_coating</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_coating</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
@@ -2501,6 +3165,16 @@
           <t>使用帮助卡时随机伤害</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_launcher</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_launcher</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
@@ -2518,6 +3192,16 @@
           <t>使用帮助卡时恢复2点血量</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_recycler</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_recycler</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
@@ -2535,6 +3219,16 @@
           <t>使用帮助卡时随机触发九选一</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_slot_machine</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_slot_machine</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
@@ -2552,6 +3246,16 @@
           <t>击杀精英/层主时加入金币卡</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>visual.face.relic.lucky_coin</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.lucky_coin</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
@@ -2569,6 +3273,16 @@
           <t>致命伤害免死</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>visual.face.relic.phoenix_feather</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.phoenix_feather</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
@@ -2586,6 +3300,16 @@
           <t>每关卡开始加入两张恢复药水</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>visual.face.relic.potion_bag</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.potion_bag</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
@@ -2603,6 +3327,16 @@
           <t>击杀怪物时获得护甲</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>visual.face.relic.shield_knife</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.shield_knife</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
@@ -2620,6 +3354,16 @@
           <t>击杀怪物时随机伤害</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>visual.face.relic.sling</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.sling</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
@@ -2637,6 +3381,16 @@
           <t>每关卡开始加入两张飞刀</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>visual.face.relic.throwing_knife_bag</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.throwing_knife_bag</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
@@ -2654,6 +3408,16 @@
           <t>血量上限+6，关卡结束恢复6</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>visual.face.relic.vitality_amulet</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.vitality_amulet</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
@@ -2671,6 +3435,16 @@
           <t>血量上限+2，木套装额外+8</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>visual.face.relic.wood_armor</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.wood_armor</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
@@ -2688,6 +3462,16 @@
           <t>基础护甲+1，木套装额外+2</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>visual.face.relic.wood_shield</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.wood_shield</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
@@ -2705,6 +3489,16 @@
           <t>攻击+1，木套装额外+2</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>visual.face.relic.wood_sword</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.wood_sword</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
@@ -2722,6 +3516,11 @@
           <t>温泉房</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>visual.icon.Fountain</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
@@ -2739,6 +3538,11 @@
           <t>金币房</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>visual.icon.Gold</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
@@ -2756,6 +3560,11 @@
           <t>商店</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>visual.icon.Shop</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
@@ -2773,6 +3582,11 @@
           <t>酒馆</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>visual.icon.Tavern</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
@@ -2790,6 +3604,11 @@
           <t>宝箱房</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>visual.icon.Treasure</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
@@ -2807,6 +3626,16 @@
           <t>相邻怪物被移除时获得其移除前攻击和护甲</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>visual.face.skill.absorb_bone</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.absorb_bone</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
@@ -2824,6 +3653,16 @@
           <t>每次移动吸取相邻怪物全部护甲</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>visual.face.skill.absorb_stone</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.absorb_stone</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
@@ -2841,6 +3680,16 @@
           <t>移动到角格时对玩家造成2点伤害</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>visual.face.skill.air_strike</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.air_strike</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
@@ -2858,6 +3707,16 @@
           <t>关卡结束加入飞刀/爆弹/破击锤之一</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>visual.face.skill.arsenal</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.arsenal</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
@@ -2875,6 +3734,16 @@
           <t>战斗时攻击+2，换敌复原</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>visual.face.skill.battle_hardened</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.battle_hardened</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
@@ -2892,6 +3761,16 @@
           <t>每移动5次洗入乞丐</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>visual.face.skill.beggar_bond</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.beggar_bond</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
@@ -2909,6 +3788,16 @@
           <t>下一次受到伤害时，该次伤害变为0</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>visual.face.skill.blessing</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.blessing</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="B128" t="inlineStr">
@@ -2926,6 +3815,16 @@
           <t>战斗时每造成2点伤害，本卡攻击+1</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>visual.face.skill.bloodthirst</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.bloodthirst</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
@@ -2943,6 +3842,16 @@
           <t>每移动3次放烈焰</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>visual.face.skill.breathe_fire</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.breathe_fire</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="B130" t="inlineStr">
@@ -2960,6 +3869,16 @@
           <t>每移动3次加入龙信徒</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>visual.face.skill.call_followers</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.call_followers</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
@@ -2977,6 +3896,16 @@
           <t>每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>visual.face.skill.delivery</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.delivery</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
@@ -2994,6 +3923,16 @@
           <t>被移除时加入烈焰</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>visual.face.skill.devotion</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.devotion</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="B133" t="inlineStr">
@@ -3011,6 +3950,16 @@
           <t>关卡结束白色帮助卡三选一</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>visual.face.skill.easy_road</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.easy_road</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="B134" t="inlineStr">
@@ -3028,6 +3977,16 @@
           <t>对偶数等级怪物造成双倍伤害</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>visual.face.skill.even_hatred</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.even_hatred</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="B135" t="inlineStr">
@@ -3045,6 +4004,16 @@
           <t>被移除时洗入骷髅头与无头骷髅</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fall_apart</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fall_apart</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="B136" t="inlineStr">
@@ -3062,6 +4031,16 @@
           <t>累计损失10护甲洗入石人</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>visual.face.skill.falling_rocks</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.falling_rocks</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="B137" t="inlineStr">
@@ -3079,6 +4058,16 @@
           <t>相邻玩家与其他怪物战斗时改为与本卡战斗</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fight_me</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fight_me</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
@@ -3096,6 +4085,16 @@
           <t>福地达到3后下一次移动造成99伤害</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>visual.face.skill.find_weakness</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.find_weakness</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="B139" t="inlineStr">
@@ -3113,6 +4112,16 @@
           <t>每有一张烈焰，本卡攻击+2</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fire_power</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fire_power</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="B140" t="inlineStr">
@@ -3130,6 +4139,16 @@
           <t>持有先攻技能</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>visual.face.skill.first_strike</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.first_strike</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="B141" t="inlineStr">
@@ -3147,6 +4166,16 @@
           <t>烈焰帮助卡造成的伤害+1</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>visual.face.skill.flame_boiling</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.flame_boiling</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
@@ -3164,6 +4193,16 @@
           <t>每移动4次移除其他普通怪物并按数量加入烈焰</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>visual.face.skill.flame_breath</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.flame_breath</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="B143" t="inlineStr">
@@ -3181,6 +4220,16 @@
           <t>被移除时洗入多骨虫和等级2随机怪物</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fracture_fall_apart</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fracture_fall_apart</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="B144" t="inlineStr">
@@ -3198,6 +4247,16 @@
           <t>每移动2次随机强化其他怪物</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>visual.face.skill.gear_delivery</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.gear_delivery</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="B145" t="inlineStr">
@@ -3215,6 +4274,16 @@
           <t>每移动3次放旋转轮</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>visual.face.skill.gift</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.gift</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="B146" t="inlineStr">
@@ -3232,6 +4301,16 @@
           <t>登场在偶数边位时伤害玩家</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>visual.face.skill.give_punch</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.give_punch</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="B147" t="inlineStr">
@@ -3249,6 +4328,16 @@
           <t>每移动3次创建福地，怪物进入福地获得护甲和攻击</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>visual.face.skill.guide</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.guide</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="B148" t="inlineStr">
@@ -3266,6 +4355,16 @@
           <t>左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hard</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hard</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="B149" t="inlineStr">
@@ -3283,6 +4382,16 @@
           <t>血量上限+10，关卡结束恢复10</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hard_skin</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hard_skin</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="B150" t="inlineStr">
@@ -3300,6 +4409,16 @@
           <t>每次移动到格1时对玩家造成2点伤害</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hoodlum</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hoodlum</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
@@ -3317,6 +4436,16 @@
           <t>怪物卡因怪物技能位移时伤害玩家</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hot_observation</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hot_observation</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
@@ -3334,6 +4463,16 @@
           <t>每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>visual.face.skill.intense_burning</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.intense_burning</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="B153" t="inlineStr">
@@ -3351,6 +4490,16 @@
           <t>其他怪物获得攻击时本卡攻击+1</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>visual.face.skill.learning_growth</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.learning_growth</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
@@ -3368,6 +4517,16 @@
           <t>有烈焰时攻击+4</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>visual.face.skill.love_fire</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.love_fire</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
@@ -3385,6 +4544,16 @@
           <t>每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>visual.face.skill.mixed_bones</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.mixed_bones</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="B156" t="inlineStr">
@@ -3402,6 +4571,16 @@
           <t>战斗时本卡攻击+2</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>visual.face.skill.monster_battle_hardened</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.monster_battle_hardened</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
@@ -3419,6 +4598,16 @@
           <t>每移动1次，相邻怪物攻击+1</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>visual.face.skill.orc_tactics</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.orc_tactics</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
@@ -3436,6 +4625,16 @@
           <t>每移动9次从其他怪物牌组加入普通怪物</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>visual.face.skill.otherworld_help</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.otherworld_help</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="B159" t="inlineStr">
@@ -3453,6 +4652,16 @@
           <t>每移动3次与随机帮助卡交换</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>visual.face.skill.random_walk</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.random_walk</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="B160" t="inlineStr">
@@ -3470,6 +4679,16 @@
           <t>所有怪物卡视为与本卡正交相邻</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>visual.face.skill.range_expand</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.range_expand</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="B161" t="inlineStr">
@@ -3487,6 +4706,16 @@
           <t>每损失3点护甲，相邻怪物攻击+1</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>visual.face.skill.rascality</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.rascality</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="B162" t="inlineStr">
@@ -3504,6 +4733,16 @@
           <t>相邻无头骷髅组合</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>visual.face.skill.recombine_body</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.recombine_body</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="B163" t="inlineStr">
@@ -3521,6 +4760,16 @@
           <t>相邻骷髅头组合</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>visual.face.skill.recombine_head</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.recombine_head</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="B164" t="inlineStr">
@@ -3538,6 +4787,16 @@
           <t>移动到玩家相邻格时强制战斗</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>visual.face.skill.relentless_chase</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.relentless_chase</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="B165" t="inlineStr">
@@ -3555,6 +4814,16 @@
           <t>移动到格3时移除格6帮助卡</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>visual.face.skill.rolling_crush</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.rolling_crush</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="B166" t="inlineStr">
@@ -3572,6 +4841,16 @@
           <t>每移动3次旋转</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>visual.face.skill.rotate_lover</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.rotate_lover</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="B167" t="inlineStr">
@@ -3589,6 +4868,16 @@
           <t>每移动2次，移除九宫格上所有的龙信徒</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>visual.face.skill.sacrifice</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.sacrifice</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="B168" t="inlineStr">
@@ -3606,6 +4895,16 @@
           <t>护甲归零时伤害玩家</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>visual.face.skill.sharp_stone</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.sharp_stone</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="B169" t="inlineStr">
@@ -3623,6 +4922,16 @@
           <t>每次获得攻击时，本卡额外攻击+1且不递归</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>visual.face.skill.smart</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.smart</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="B170" t="inlineStr">
@@ -3640,6 +4949,16 @@
           <t>玩家与本卡战斗后旋转一次</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>visual.face.skill.space_mastery</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.space_mastery</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="B171" t="inlineStr">
@@ -3657,6 +4976,16 @@
           <t>累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stocking</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stocking</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="B172" t="inlineStr">
@@ -3674,6 +5003,16 @@
           <t>移动到左列时其他怪物获得2点护甲</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stone_growth</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stone_growth</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="B173" t="inlineStr">
@@ -3691,6 +5030,16 @@
           <t>玩家卡和怪物卡损失护甲时本卡攻击+1</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stone_lover</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stone_lover</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="B174" t="inlineStr">
@@ -3708,6 +5057,16 @@
           <t>其他怪物卡受到的伤害减少1点</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stone_shelter</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stone_shelter</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="B175" t="inlineStr">
@@ -3725,6 +5084,16 @@
           <t>格6攻击+2并获得先攻</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stray_cub</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stray_cub</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="B176" t="inlineStr">
@@ -3742,6 +5111,16 @@
           <t>每移动1次攻击+2</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stroll</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stroll</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="B177" t="inlineStr">
@@ -3759,6 +5138,16 @@
           <t>移动时与相邻两张怪物合成为巨大骷髅</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>visual.face.skill.strong_combo</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.strong_combo</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="B178" t="inlineStr">
@@ -3776,6 +5165,16 @@
           <t>战斗时恢复1且攻击+1</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>visual.face.skill.survival_wisdom</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.survival_wisdom</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="B179" t="inlineStr">
@@ -3793,6 +5192,16 @@
           <t>每移动2次吸相邻怪物护甲</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>visual.face.skill.swallow_stone</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.swallow_stone</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="B180" t="inlineStr">
@@ -3810,6 +5219,16 @@
           <t>相邻时只能与本卡战斗</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>visual.face.skill.taunt</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.taunt</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="B181" t="inlineStr">
@@ -3827,6 +5246,16 @@
           <t>每移动3次移除相邻帮助卡</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>visual.face.skill.thief_claims</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.thief_claims</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="B182" t="inlineStr">
@@ -3844,6 +5273,16 @@
           <t>战斗时对怪物造成等同其攻击的伤害</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>visual.face.skill.thorn_skin</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.thorn_skin</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="B183" t="inlineStr">
@@ -3861,6 +5300,16 @@
           <t>每移动2次消耗本卡2护甲并伤害玩家</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>visual.face.skill.throw_stone</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.throw_stone</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="B184" t="inlineStr">
@@ -3878,6 +5327,16 @@
           <t>关卡开始放入倍增塔</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>visual.face.skill.tower_child</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.tower_child</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="B185" t="inlineStr">
@@ -3895,6 +5354,16 @@
           <t>登场旋转一次</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>visual.face.skill.turn_world</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.turn_world</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="B186" t="inlineStr">
@@ -3912,6 +5381,16 @@
           <t>每移动3次随机交换怪物</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>visual.face.skill.unstable</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.unstable</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="B187" t="inlineStr">
@@ -3929,6 +5408,16 @@
           <t>每移动2次，移除相邻格子上的怪物卡和帮助卡</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>visual.face.skill.violence_maniac</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.violence_maniac</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="B188" t="inlineStr">
@@ -3944,6 +5433,16 @@
       <c r="D188" t="inlineStr">
         <is>
           <t>依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>visual.face.skill.violence_nutrition</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.violence_nutrition</t>
         </is>
       </c>
     </row>

--- a/Assets/Tools/Luban/Datas/content_visual.xlsx
+++ b/Assets/Tools/Luban/Datas/content_visual.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[使用时] 将目标怪物卡护甲降低10点</t>
+          <t>破击锤：[使用时] 将目标怪物卡护甲降低10点</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[场上] 当正交相邻格补牌为怪物卡时，对其造成10点伤害，之后移除本卡</t>
+          <t>捕熊陷阱：[场上] 当正交相邻格补牌为怪物卡时，对其造成10点伤害，之后移除本卡</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[使用时] 扣除5点血量上限并随机获得攻击+1、护甲+1、50金币或随机遗物</t>
+          <t>血液转换：[使用时] 扣除5点血量上限并随机获得攻击+1、护甲+1、50金币或随机遗物</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[使用时] 从三个遗物中选择一个获得</t>
+          <t>蓝色宝箱卡：[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[使用时] 对所有怪物卡造成4点伤害</t>
+          <t>爆弹：[使用时] 对所有怪物卡造成4点伤害</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[使用时] 玩家下一次对怪物造成的战斗伤害翻倍</t>
+          <t>暴力卡：[使用时] 玩家下一次对怪物造成的战斗伤害翻倍</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[使用时] 从三个遗物中选择一个获得</t>
+          <t>普通宝箱卡：[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[场上] 处于格1时，对怪物卡使用的帮助卡触发两次；[道具牌格] 对玩家卡使用的帮助卡生效两次，触发后永久移除本卡</t>
+          <t>倍增塔：[场上] 处于格1时，对怪物卡使用的帮助卡触发两次；[道具牌格] 对玩家卡使用的帮助卡生效两次，触发后永久移除本卡</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[使用时] 对目标怪物卡造成等同于玩家攻击的伤害</t>
+          <t>火球术：[使用时] 对目标怪物卡造成等同于玩家攻击的伤害</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[使用时] 对玩家造成4点伤害并永久移除本卡</t>
+          <t>烈焰：[使用时] 对玩家造成4点伤害并永久移除本卡</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[使用时] 将玩家卡血量回满</t>
+          <t>食品卡：[使用时] 将玩家卡血量回满</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[使用时] 为玩家提供50金币</t>
+          <t>金币卡：[使用时] 为玩家提供50金币</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[使用时] 从三个遗物中选择一个获得</t>
+          <t>金色宝箱卡：[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[使用时] 恢复10点血量</t>
+          <t>恢复药水：[使用时] 恢复10点血量</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[场上] 移动到玩家卡正交相邻格时，为玩家恢复2点血量；[道具牌格] 玩家与怪物战斗时，恢复1点血量；[使用时] 直接移除本卡，不触发其他效果</t>
+          <t>治疗泉：[场上] 移动到玩家卡正交相邻格时，为玩家恢复2点血量；[道具牌格] 玩家与怪物战斗时，恢复1点血量；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[使用时] 对目标怪物卡造成等同于玩家当前血量的伤害</t>
+          <t>撞击教程：[使用时] 对目标怪物卡造成等同于玩家当前血量的伤害</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[使用时] 移除一张非精英非层主怪物卡，并获得等同于其当前护甲的护甲</t>
+          <t>绑票：[使用时] 移除一张非精英非层主怪物卡，并获得等同于其当前护甲的护甲</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[场上] 移动到格3时，若格6为非精英非层主怪物，则移除该怪物和本卡；[使用时] 直接移除本卡，不触发其他效果</t>
+          <t>滚石：[场上] 移动到格3时，若格6为非精英非层主怪物，则移除该怪物和本卡；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[使用时] 逆时针旋转一次</t>
+          <t>旋转轮：[使用时] 逆时针旋转一次</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[使用时] 对目标怪物卡造成等同于玩家当前护甲的伤害</t>
+          <t>盾击教程：[使用时] 对目标怪物卡造成等同于玩家当前护甲的伤害</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[使用时] 选择攻击+1、护甲+1或血量上限与当前血量+2</t>
+          <t>属性提升卡：[使用时] 选择攻击+1、护甲+1或血量上限与当前血量+2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[使用时] 玩家获得5点护甲</t>
+          <t>耐用盾牌：[使用时] 玩家获得5点护甲</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[使用时] 选择除玩家卡外的两张卡牌互换所在格子位置</t>
+          <t>交换卡：[使用时] 选择除玩家卡外的两张卡牌互换所在格子位置</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[使用时] 选择除玩家卡外的一张卡牌洗回战斗卡组</t>
+          <t>传送卡：[使用时] 选择除玩家卡外的一张卡牌洗回战斗卡组</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[使用时] 对目标怪物卡造成6点伤害</t>
+          <t>飞刀：[使用时] 对目标怪物卡造成6点伤害</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[使用时] 下一次玩家受到伤害时，该次伤害变为0</t>
+          <t>庇佑魔法卡：[使用时] 下一次玩家受到伤害时，该次伤害变为0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[场上] 移动到角格时，对随机怪物造成3点伤害；触发4次后移除本卡；[道具牌格] 玩家与怪物战斗时，对随机一张怪物卡造成2点伤害；[使用时] 直接移除本卡，不触发其他效果</t>
+          <t>瞭望塔：[场上] 移动到角格时，对随机怪物造成3点伤害；触发4次后移除本卡；[道具牌格] 玩家与怪物战斗时，对随机一张怪物卡造成2点伤害；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>每移动5次洗入乞丐</t>
+          <t>乞丐：每移动5次洗入乞丐</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>相邻玩家与其他怪物战斗时改为与本卡战斗</t>
+          <t>兽人大只佬：相邻玩家与其他怪物战斗时改为与本卡战斗</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>被移除时洗入骷髅头与无头骷髅</t>
+          <t>大骷髅：被移除时洗入骷髅头与无头骷髅</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>左列战斗时按损失护甲伤害玩家</t>
+          <t>大石头：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1379,6 +1379,11 @@
           <t>Monster</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>骨棒骷髅</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>visual.face.monster.bone_club_skeleton</t>
@@ -1403,7 +1408,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
+          <t>骨头快递员：每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1430,7 +1435,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>战斗时本卡攻击+2</t>
+          <t>无脑兽人：战斗时本卡攻击+2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>每移动3次加入龙信徒</t>
+          <t>龙教主：每移动3次加入龙信徒</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1484,7 +1489,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>被移除时加入烈焰</t>
+          <t>龙信徒：被移除时加入烈焰</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1511,7 +1516,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>每移动2次，移除九宫格上所有的龙信徒</t>
+          <t>刽子手：每移动2次，移除九宫格上所有的龙信徒</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1538,7 +1543,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>有烈焰时攻击+4</t>
+          <t>浴火者：有烈焰时攻击+4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1565,7 +1570,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
+          <t>火教主：每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1592,7 +1597,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>每移动4次移除其他普通怪物并按数量加入烈焰；烈焰帮助卡造成的伤害+1</t>
+          <t>火龙：每移动4次移除其他普通怪物并按数量加入烈焰；烈焰帮助卡造成的伤害+1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1619,7 +1624,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>每有一张烈焰，本卡攻击+2</t>
+          <t>火焰祭司：每有一张烈焰，本卡攻击+2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1646,7 +1651,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>左列战斗时按损失护甲伤害玩家</t>
+          <t>吞火者：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1673,7 +1678,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>每移动3次放旋转轮</t>
+          <t>友好的远古生物：每移动3次放旋转轮</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1700,7 +1705,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>被移除时洗入多骨虫和等级2随机怪物</t>
+          <t>巨大骷髅：被移除时洗入多骨虫和等级2随机怪物</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1727,7 +1732,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>移动到左列时其他怪物获得2点护甲</t>
+          <t>增生石块：移动到左列时其他怪物获得2点护甲</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1754,7 +1759,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>相邻骷髅头组合</t>
+          <t>无头骷髅：相邻骷髅头组合</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1781,7 +1786,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>每次移动到格1时对玩家造成2点伤害</t>
+          <t>混混：每次移动到格1时对玩家造成2点伤害</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1808,7 +1813,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>移动到玩家相邻格时强制战斗</t>
+          <t>杀手：移动到玩家相邻格时强制战斗</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>每次移动吸取相邻怪物全部护甲；累计损失10护甲洗入石人</t>
+          <t>巨石人：每次移动吸取相邻怪物全部护甲；累计损失10护甲洗入石人</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1862,7 +1867,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>每移动1次攻击+2</t>
+          <t>迷雾：每移动1次攻击+2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1889,7 +1894,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>移动时与相邻两张怪物合成为巨大骷髅</t>
+          <t>多骨虫：移动时与相邻两张怪物合成为巨大骷髅</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1916,7 +1921,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>怪物卡因怪物技能位移时伤害玩家</t>
+          <t>观察者：怪物卡因怪物技能位移时伤害玩家</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1943,7 +1948,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>战斗时恢复1且攻击+1</t>
+          <t>年迈兽人：战斗时恢复1且攻击+1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1970,7 +1975,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>每移动2次，移除相邻格子上的怪物卡和帮助卡；依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
+          <t>兽人老大：每移动2次，移除相邻格子上的怪物卡和帮助卡；依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1997,7 +2002,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>每移动1次，相邻怪物攻击+1</t>
+          <t>兽人指挥官：每移动1次，相邻怪物攻击+1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2024,7 +2029,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>每移动2次随机强化其他怪物</t>
+          <t>兽人军需官：每移动2次随机强化其他怪物</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2051,7 +2056,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>战斗时每造成2点伤害，本卡攻击+1</t>
+          <t>兽人战士：战斗时每造成2点伤害，本卡攻击+1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2078,7 +2083,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>每移动3次移除相邻帮助卡</t>
+          <t>扒手：每移动3次移除相邻帮助卡</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2105,7 +2110,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>每移动3次创建福地，怪物进入福地获得护甲和攻击；福地达到3后下一次移动造成99伤害</t>
+          <t>领头人：每移动3次创建福地，怪物进入福地获得护甲和攻击；福地达到3后下一次移动造成99伤害</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2132,7 +2137,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>每损失3点护甲，相邻怪物攻击+1</t>
+          <t>流氓：每损失3点护甲，相邻怪物攻击+1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2159,7 +2164,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>移动到格3时移除格6帮助卡</t>
+          <t>滚石人：移动到格3时移除格6帮助卡</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2186,7 +2191,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>每移动3次旋转</t>
+          <t>旋转幼崽：每移动3次旋转</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2213,7 +2218,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>每移动3次放烈焰</t>
+          <t>火蜥蜴：每移动3次放烈焰</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2240,7 +2245,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>护甲归零时伤害玩家</t>
+          <t>尖石：护甲归零时伤害玩家</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2267,7 +2272,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>其他怪物卡受到的伤害减少1点</t>
+          <t>庇护石：其他怪物卡受到的伤害减少1点</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2294,7 +2299,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>相邻怪物被移除时获得其移除前攻击和护甲；每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
+          <t>骷髅王：相邻怪物被移除时获得其移除前攻击和护甲；每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2321,7 +2326,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>所有怪物卡视为与本卡正交相邻</t>
+          <t>骷髅法师：所有怪物卡视为与本卡正交相邻</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2348,7 +2353,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>相邻时只能与本卡战斗</t>
+          <t>骷髅嘲讽子：相邻时只能与本卡战斗</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2375,7 +2380,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>相邻无头骷髅组合</t>
+          <t>骷髅头：相邻无头骷髅组合</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2402,7 +2407,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>移动到角格时对玩家造成2点伤害</t>
+          <t>空中巨眼：移动到角格时对玩家造成2点伤害</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2429,7 +2434,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>每次获得攻击时，本卡额外攻击+1且不递归</t>
+          <t>聪明兽人：每次获得攻击时，本卡额外攻击+1且不递归</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2456,7 +2461,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
+          <t>走私者：累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2483,7 +2488,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>玩家与本卡战斗后旋转一次；每移动9次从其他怪物牌组加入普通怪物</t>
+          <t>空间大师：玩家与本卡战斗后旋转一次；每移动9次从其他怪物牌组加入普通怪物</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2510,7 +2515,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>每移动3次与随机帮助卡交换</t>
+          <t>踏步行者：每移动3次与随机帮助卡交换</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2535,6 +2540,11 @@
           <t>Monster</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>石傀儡</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>visual.face.monster.stone_golem</t>
@@ -2557,6 +2567,11 @@
           <t>Monster</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>石头人</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>visual.face.monster.stone_man</t>
@@ -2581,7 +2596,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>玩家卡和怪物卡损失护甲时本卡攻击+1</t>
+          <t>石虾：玩家卡和怪物卡损失护甲时本卡攻击+1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2608,7 +2623,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>每移动2次吸相邻怪物护甲</t>
+          <t>吞石者：每移动2次吸相邻怪物护甲</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2635,7 +2650,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>每移动2次消耗本卡2护甲并伤害玩家</t>
+          <t>丢石人：每移动2次消耗本卡2护甲并伤害玩家</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2662,7 +2677,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>登场在偶数边位时伤害玩家</t>
+          <t>打手：登场在偶数边位时伤害玩家</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2687,6 +2702,11 @@
           <t>Monster</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>流浪汉</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>visual.face.monster.vagrant</t>
@@ -2709,6 +2729,11 @@
           <t>Monster</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>历战兽人</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>visual.face.monster.veteran_orc</t>
@@ -2733,7 +2758,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>每移动3次随机交换怪物</t>
+          <t>虚空幼崽：每移动3次随机交换怪物</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2758,6 +2783,11 @@
           <t>Monster</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>误入虚空者</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>visual.face.monster.void_lost</t>
@@ -2782,7 +2812,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>格6攻击+2并获得先攻</t>
+          <t>流浪孩童：格6攻击+2并获得先攻</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2809,7 +2839,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>登场旋转一次</t>
+          <t>转动世界的手：登场旋转一次</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2836,7 +2866,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>其他怪物获得攻击时本卡攻击+1</t>
+          <t>年轻兽人：其他怪物获得攻击时本卡攻击+1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3000,7 +3030,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>所有恢复血量效果翻倍</t>
+          <t>渴望：所有恢复血量效果翻倍</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3027,7 +3057,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>所有怪物攻击-1</t>
+          <t>龙鳞甲：所有怪物攻击-1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3054,7 +3084,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>金币抵消护甲伤害</t>
+          <t>金币盔甲：金币抵消护甲伤害</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>击杀怪物时获得2金币</t>
+          <t>打金刀：击杀怪物时获得2金币</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3108,7 +3138,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>基础护甲+1，按基础护甲补当前护甲</t>
+          <t>重盔甲：基础护甲+1，按基础护甲补当前护甲</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3135,7 +3165,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>使用帮助卡时获得护甲</t>
+          <t>废物涂层：使用帮助卡时获得护甲</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3162,7 +3192,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>使用帮助卡时随机伤害</t>
+          <t>废物发射器：使用帮助卡时随机伤害</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3189,7 +3219,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>使用帮助卡时恢复2点血量</t>
+          <t>废物利用机：使用帮助卡时恢复2点血量</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3216,7 +3246,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>使用帮助卡时随机触发九选一</t>
+          <t>废物老虎机：使用帮助卡时随机触发九选一</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3243,7 +3273,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>击杀精英/层主时加入金币卡</t>
+          <t>幸运硬币：击杀精英/层主时加入金币卡</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3270,7 +3300,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>致命伤害免死</t>
+          <t>凤凰羽毛：致命伤害免死</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3297,7 +3327,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>每关卡开始加入两张恢复药水</t>
+          <t>药水袋：每关卡开始加入两张恢复药水</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3324,7 +3354,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>击杀怪物时获得护甲</t>
+          <t>打盾刀：击杀怪物时获得护甲</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3351,7 +3381,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>击杀怪物时随机伤害</t>
+          <t>弹弓：击杀怪物时随机伤害</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3378,7 +3408,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>每关卡开始加入两张飞刀</t>
+          <t>飞刀袋：每关卡开始加入两张飞刀</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3405,7 +3435,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>血量上限+6，关卡结束恢复6</t>
+          <t>活力护符：血量上限+6，关卡结束恢复6</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3432,7 +3462,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>血量上限+2，木套装额外+8</t>
+          <t>木甲：血量上限+2，木套装额外+8</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3459,7 +3489,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>基础护甲+1，木套装额外+2</t>
+          <t>木盾：基础护甲+1，木套装额外+2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3486,7 +3516,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>攻击+1，木套装额外+2</t>
+          <t>木剑：攻击+1，木套装额外+2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3623,7 +3653,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>相邻怪物被移除时获得其移除前攻击和护甲</t>
+          <t>吸骨：相邻怪物被移除时获得其移除前攻击和护甲</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3650,7 +3680,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>每次移动吸取相邻怪物全部护甲</t>
+          <t>吸石：每次移动吸取相邻怪物全部护甲</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3677,7 +3707,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>移动到角格时对玩家造成2点伤害</t>
+          <t>空中打击：移动到角格时对玩家造成2点伤害</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3704,7 +3734,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>关卡结束加入飞刀/爆弹/破击锤之一</t>
+          <t>军械库：关卡结束加入飞刀/爆弹/破击锤之一</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3731,7 +3761,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>战斗时攻击+2，换敌复原</t>
+          <t>历战：战斗时攻击+2，换敌复原</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3758,7 +3788,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>每移动5次洗入乞丐</t>
+          <t>丐帮同心：每移动5次洗入乞丐</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3785,7 +3815,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>下一次受到伤害时，该次伤害变为0</t>
+          <t>庇佑：下一次受到伤害时，该次伤害变为0</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3812,7 +3842,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>战斗时每造成2点伤害，本卡攻击+1</t>
+          <t>嗜血：战斗时每造成2点伤害，本卡攻击+1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3839,7 +3869,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>每移动3次放烈焰</t>
+          <t>喷火：每移动3次放烈焰</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3866,7 +3896,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>每移动3次加入龙信徒</t>
+          <t>呼唤信徒：每移动3次加入龙信徒</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3893,7 +3923,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
+          <t>快递：每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3920,7 +3950,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>被移除时加入烈焰</t>
+          <t>献身：被移除时加入烈焰</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3947,7 +3977,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>关卡结束白色帮助卡三选一</t>
+          <t>轻车熟路：关卡结束白色帮助卡三选一</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -3974,7 +4004,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>对偶数等级怪物造成双倍伤害</t>
+          <t>偶数仇恨：对偶数等级怪物造成双倍伤害</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4001,7 +4031,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>被移除时洗入骷髅头与无头骷髅</t>
+          <t>散架：被移除时洗入骷髅头与无头骷髅</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4028,7 +4058,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>累计损失10护甲洗入石人</t>
+          <t>落石：累计损失10护甲洗入石人</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4055,7 +4085,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>相邻玩家与其他怪物战斗时改为与本卡战斗</t>
+          <t>和我打！：相邻玩家与其他怪物战斗时改为与本卡战斗</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4082,7 +4112,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>福地达到3后下一次移动造成99伤害</t>
+          <t>发现弱点：福地达到3后下一次移动造成99伤害</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4109,7 +4139,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>每有一张烈焰，本卡攻击+2</t>
+          <t>火之力：每有一张烈焰，本卡攻击+2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4136,7 +4166,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>持有先攻技能</t>
+          <t>先攻：持有先攻技能</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4163,7 +4193,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>烈焰帮助卡造成的伤害+1</t>
+          <t>烈焰沸腾：烈焰帮助卡造成的伤害+1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4190,7 +4220,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>每移动4次移除其他普通怪物并按数量加入烈焰</t>
+          <t>烈焰吐息：每移动4次移除其他普通怪物并按数量加入烈焰</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4217,7 +4247,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>被移除时洗入多骨虫和等级2随机怪物</t>
+          <t>折损散架：被移除时洗入多骨虫和等级2随机怪物</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4244,7 +4274,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>每移动2次随机强化其他怪物</t>
+          <t>发装备了！：每移动2次随机强化其他怪物</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4271,7 +4301,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>每移动3次放旋转轮</t>
+          <t>礼物：每移动3次放旋转轮</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4298,7 +4328,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>登场在偶数边位时伤害玩家</t>
+          <t>给你一拳：登场在偶数边位时伤害玩家</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4325,7 +4355,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>每移动3次创建福地，怪物进入福地获得护甲和攻击</t>
+          <t>引路：每移动3次创建福地，怪物进入福地获得护甲和攻击</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4352,7 +4382,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>左列战斗时按损失护甲伤害玩家</t>
+          <t>坚硬：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4379,7 +4409,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>血量上限+10，关卡结束恢复10</t>
+          <t>硬皮：血量上限+10，关卡结束恢复10</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4406,7 +4436,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>每次移动到格1时对玩家造成2点伤害</t>
+          <t>混的人：每次移动到格1时对玩家造成2点伤害</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4433,7 +4463,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>怪物卡因怪物技能位移时伤害玩家</t>
+          <t>灼热观察：怪物卡因怪物技能位移时伤害玩家</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4460,7 +4490,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
+          <t>剧烈燃烧：每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4487,7 +4517,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>其他怪物获得攻击时本卡攻击+1</t>
+          <t>学习成长：其他怪物获得攻击时本卡攻击+1</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4514,7 +4544,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>有烈焰时攻击+4</t>
+          <t>恋火：有烈焰时攻击+4</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4541,7 +4571,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
+          <t>混合骨头：每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4568,7 +4598,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>战斗时本卡攻击+2</t>
+          <t>历战怪物：战斗时本卡攻击+2</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4595,7 +4625,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>每移动1次，相邻怪物攻击+1</t>
+          <t>兽人战术：每移动1次，相邻怪物攻击+1</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4622,7 +4652,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>每移动9次从其他怪物牌组加入普通怪物</t>
+          <t>异界帮助：每移动9次从其他怪物牌组加入普通怪物</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4649,7 +4679,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>每移动3次与随机帮助卡交换</t>
+          <t>乱步：每移动3次与随机帮助卡交换</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4676,7 +4706,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>所有怪物卡视为与本卡正交相邻</t>
+          <t>范围扩大：所有怪物卡视为与本卡正交相邻</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4703,7 +4733,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>每损失3点护甲，相邻怪物攻击+1</t>
+          <t>痞气：每损失3点护甲，相邻怪物攻击+1</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4730,7 +4760,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>相邻无头骷髅组合</t>
+          <t>重新组合身：相邻无头骷髅组合</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4757,7 +4787,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>相邻骷髅头组合</t>
+          <t>重新组合头：相邻骷髅头组合</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4784,7 +4814,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>移动到玩家相邻格时强制战斗</t>
+          <t>不休追击：移动到玩家相邻格时强制战斗</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4811,7 +4841,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>移动到格3时移除格6帮助卡</t>
+          <t>滚动碾压：移动到格3时移除格6帮助卡</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4838,7 +4868,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>每移动3次旋转</t>
+          <t>爱好旋转：每移动3次旋转</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4865,7 +4895,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>每移动2次，移除九宫格上所有的龙信徒</t>
+          <t>献祭：每移动2次，移除九宫格上所有的龙信徒</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4892,7 +4922,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>护甲归零时伤害玩家</t>
+          <t>尖石：护甲归零时伤害玩家</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4919,7 +4949,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>每次获得攻击时，本卡额外攻击+1且不递归</t>
+          <t>大聪明：每次获得攻击时，本卡额外攻击+1且不递归</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4946,7 +4976,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>玩家与本卡战斗后旋转一次</t>
+          <t>空间掌握：玩家与本卡战斗后旋转一次</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -4973,7 +5003,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
+          <t>进货：累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5000,7 +5030,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>移动到左列时其他怪物获得2点护甲</t>
+          <t>石增长：移动到左列时其他怪物获得2点护甲</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5027,7 +5057,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>玩家卡和怪物卡损失护甲时本卡攻击+1</t>
+          <t>石头爱好者：玩家卡和怪物卡损失护甲时本卡攻击+1</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5054,7 +5084,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>其他怪物卡受到的伤害减少1点</t>
+          <t>石庇护：其他怪物卡受到的伤害减少1点</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5081,7 +5111,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>格6攻击+2并获得先攻</t>
+          <t>流浪幼崽：格6攻击+2并获得先攻</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5108,7 +5138,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>每移动1次攻击+2</t>
+          <t>漫步：每移动1次攻击+2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5135,7 +5165,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>移动时与相邻两张怪物合成为巨大骷髅</t>
+          <t>强力组合：移动时与相邻两张怪物合成为巨大骷髅</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5162,7 +5192,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>战斗时恢复1且攻击+1</t>
+          <t>生存智慧：战斗时恢复1且攻击+1</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5189,7 +5219,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>每移动2次吸相邻怪物护甲</t>
+          <t>吞石：每移动2次吸相邻怪物护甲</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5216,7 +5246,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>相邻时只能与本卡战斗</t>
+          <t>嘲讽：相邻时只能与本卡战斗</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5243,7 +5273,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>每移动3次移除相邻帮助卡</t>
+          <t>东西归我了！：每移动3次移除相邻帮助卡</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5270,7 +5300,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>战斗时对怪物造成等同其攻击的伤害</t>
+          <t>刺皮：战斗时对怪物造成等同其攻击的伤害</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5297,7 +5327,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>每移动2次消耗本卡2护甲并伤害玩家</t>
+          <t>丢石头：每移动2次消耗本卡2护甲并伤害玩家</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5324,7 +5354,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>关卡开始放入倍增塔</t>
+          <t>塔之子：关卡开始放入倍增塔</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5351,7 +5381,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>登场旋转一次</t>
+          <t>转动：登场旋转一次</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5378,7 +5408,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>每移动3次随机交换怪物</t>
+          <t>不稳定：每移动3次随机交换怪物</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5405,7 +5435,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>每移动2次，移除相邻格子上的怪物卡和帮助卡</t>
+          <t>暴力狂：每移动2次，移除相邻格子上的怪物卡和帮助卡</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5432,7 +5462,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
+          <t>暴力即养分：依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">

--- a/Assets/Tools/Luban/Datas/content_visual.xlsx
+++ b/Assets/Tools/Luban/Datas/content_visual.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:D188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="37.44140625" customWidth="1" min="2" max="2"/>
@@ -451,21 +451,6 @@
           <t>description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>face_key</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>frame_key</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>icon_key</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,21 +473,6 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -520,16 +490,6 @@
           <t>玩家化身</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>visual.face.avatar.default</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>visual.icon.avatar.default</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -547,16 +507,6 @@
           <t>破击锤：[使用时] 将目标怪物卡护甲降低10点</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>visual.face.help.armor_breaking_hammer</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>visual.icon.help.armor_breaking_hammer</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -574,16 +524,6 @@
           <t>捕熊陷阱：[场上] 当正交相邻格补牌为怪物卡时，对其造成10点伤害，之后移除本卡</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>visual.face.help.bear_trap</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>visual.icon.help.bear_trap</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -601,16 +541,6 @@
           <t>血液转换：[使用时] 扣除5点血量上限并随机获得攻击+1、护甲+1、50金币或随机遗物</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>visual.face.help.blood_conversion</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>visual.icon.help.blood_conversion</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -628,16 +558,6 @@
           <t>蓝色宝箱卡：[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>visual.face.help.blue_chest_card</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>visual.icon.help.blue_chest_card</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -655,16 +575,6 @@
           <t>爆弹：[使用时] 对所有怪物卡造成4点伤害</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>visual.face.help.bomb</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>visual.icon.help.bomb</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -682,16 +592,6 @@
           <t>暴力卡：[使用时] 玩家下一次对怪物造成的战斗伤害翻倍</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>visual.face.help.brutality_card</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>visual.icon.help.brutality_card</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -709,16 +609,6 @@
           <t>普通宝箱卡：[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>visual.face.help.common_chest_card</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>visual.icon.help.common_chest_card</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -736,16 +626,6 @@
           <t>倍增塔：[场上] 处于格1时，对怪物卡使用的帮助卡触发两次；[道具牌格] 对玩家卡使用的帮助卡生效两次，触发后永久移除本卡</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>visual.face.help.doubling_tower</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>visual.icon.help.doubling_tower</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -763,16 +643,6 @@
           <t>火球术：[使用时] 对目标怪物卡造成等同于玩家攻击的伤害</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>visual.face.help.fireball</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>visual.icon.help.fireball</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -790,16 +660,6 @@
           <t>烈焰：[使用时] 对玩家造成4点伤害并永久移除本卡</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>visual.face.help.flame</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>visual.icon.help.flame</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -817,16 +677,6 @@
           <t>食品卡：[使用时] 将玩家卡血量回满</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>visual.face.help.food_card</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>visual.icon.help.food_card</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -844,16 +694,6 @@
           <t>金币卡：[使用时] 为玩家提供50金币</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>visual.face.help.gold_card</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>visual.icon.help.gold_card</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -871,16 +711,6 @@
           <t>金色宝箱卡：[使用时] 从三个遗物中选择一个获得</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>visual.face.help.golden_chest_card</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>visual.icon.help.golden_chest_card</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -898,16 +728,6 @@
           <t>恢复药水：[使用时] 恢复10点血量</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>visual.face.help.healing_potion</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>visual.icon.help.healing_potion</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -925,16 +745,6 @@
           <t>治疗泉：[场上] 移动到玩家卡正交相邻格时，为玩家恢复2点血量；[道具牌格] 玩家与怪物战斗时，恢复1点血量；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>visual.face.help.healing_spring</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>visual.icon.help.healing_spring</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -952,16 +762,6 @@
           <t>撞击教程：[使用时] 对目标怪物卡造成等同于玩家当前血量的伤害</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>visual.face.help.impact_tutorial</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>visual.icon.help.impact_tutorial</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -979,16 +779,6 @@
           <t>绑票：[使用时] 移除一张非精英非层主怪物卡，并获得等同于其当前护甲的护甲</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>visual.face.help.kidnapping</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>visual.icon.help.kidnapping</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -1006,16 +796,6 @@
           <t>滚石：[场上] 移动到格3时，若格6为非精英非层主怪物，则移除该怪物和本卡；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>visual.face.help.rolling_stone</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>visual.icon.help.rolling_stone</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -1033,16 +813,6 @@
           <t>旋转轮：[使用时] 逆时针旋转一次</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>visual.face.help.rotation_wheel</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>visual.icon.help.rotation_wheel</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -1060,16 +830,6 @@
           <t>盾击教程：[使用时] 对目标怪物卡造成等同于玩家当前护甲的伤害</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>visual.face.help.shield_bash_tutorial</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>visual.icon.help.shield_bash_tutorial</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -1087,16 +847,6 @@
           <t>属性提升卡：[使用时] 选择攻击+1、护甲+1或血量上限与当前血量+2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>visual.face.help.stat_boost_card</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>visual.icon.help.stat_boost_card</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -1114,16 +864,6 @@
           <t>耐用盾牌：[使用时] 玩家获得5点护甲</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>visual.face.help.sturdy_shield</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>visual.icon.help.sturdy_shield</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
@@ -1141,16 +881,6 @@
           <t>交换卡：[使用时] 选择除玩家卡外的两张卡牌互换所在格子位置</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>visual.face.help.swap_card</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>visual.icon.help.swap_card</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -1168,16 +898,6 @@
           <t>传送卡：[使用时] 选择除玩家卡外的一张卡牌洗回战斗卡组</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>visual.face.help.teleport_card</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>visual.icon.help.teleport_card</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -1195,16 +915,6 @@
           <t>飞刀：[使用时] 对目标怪物卡造成6点伤害</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>visual.face.help.throwing_knife</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>visual.icon.help.throwing_knife</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -1222,16 +932,6 @@
           <t>庇佑魔法卡：[使用时] 下一次玩家受到伤害时，该次伤害变为0</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>visual.face.help.ward_magic_card</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>visual.icon.help.ward_magic_card</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -1249,16 +949,6 @@
           <t>瞭望塔：[场上] 移动到角格时，对随机怪物造成3点伤害；触发4次后移除本卡；[道具牌格] 玩家与怪物战斗时，对随机一张怪物卡造成2点伤害；[使用时] 直接移除本卡，不触发其他效果</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>visual.face.help.watchtower</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>visual.icon.help.watchtower</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -1276,16 +966,6 @@
           <t>乞丐：每移动5次洗入乞丐</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>visual.face.monster.beggar</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.beggar</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
@@ -1303,16 +983,6 @@
           <t>兽人大只佬：相邻玩家与其他怪物战斗时改为与本卡战斗</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>visual.face.monster.big_orc</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.big_orc</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -1330,16 +1000,6 @@
           <t>大骷髅：被移除时洗入骷髅头与无头骷髅</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>visual.face.monster.big_skeleton</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.big_skeleton</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -1357,16 +1017,6 @@
           <t>大石头：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>visual.face.monster.big_stone</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.big_stone</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -1384,16 +1034,6 @@
           <t>骨棒骷髅</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>visual.face.monster.bone_club_skeleton</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.bone_club_skeleton</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -1411,16 +1051,6 @@
           <t>骨头快递员：每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>visual.face.monster.bone_courier</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.bone_courier</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -1438,16 +1068,6 @@
           <t>无脑兽人：战斗时本卡攻击+2</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>visual.face.monster.brainless_orc</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.brainless_orc</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
@@ -1465,16 +1085,6 @@
           <t>龙教主：每移动3次加入龙信徒</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>visual.face.monster.dragon_cult_leader</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.dragon_cult_leader</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
@@ -1492,16 +1102,6 @@
           <t>龙信徒：被移除时加入烈焰</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>visual.face.monster.dragon_follower</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.dragon_follower</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -1519,16 +1119,6 @@
           <t>刽子手：每移动2次，移除九宫格上所有的龙信徒</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>visual.face.monster.executioner</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.executioner</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
@@ -1546,16 +1136,6 @@
           <t>浴火者：有烈焰时攻击+4</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>visual.face.monster.fire_bather</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.fire_bather</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
@@ -1573,16 +1153,6 @@
           <t>火教主：每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>visual.face.monster.fire_cult_leader</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.fire_cult_leader</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -1600,16 +1170,6 @@
           <t>火龙：每移动4次移除其他普通怪物并按数量加入烈焰；烈焰帮助卡造成的伤害+1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>visual.face.monster.fire_dragon</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.fire_dragon</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -1627,16 +1187,6 @@
           <t>火焰祭司：每有一张烈焰，本卡攻击+2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>visual.face.monster.fire_priest</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.fire_priest</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -1654,16 +1204,6 @@
           <t>吞火者：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>visual.face.monster.fire_swallower</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.fire_swallower</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -1681,16 +1221,6 @@
           <t>友好的远古生物：每移动3次放旋转轮</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>visual.face.monster.friendly_ancient</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.friendly_ancient</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -1708,16 +1238,6 @@
           <t>巨大骷髅：被移除时洗入多骨虫和等级2随机怪物</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>visual.face.monster.giant_skeleton</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.giant_skeleton</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
@@ -1735,16 +1255,6 @@
           <t>增生石块：移动到左列时其他怪物获得2点护甲</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>visual.face.monster.growing_stone</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.growing_stone</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -1762,16 +1272,6 @@
           <t>无头骷髅：相邻骷髅头组合</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>visual.face.monster.headless_skeleton</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.headless_skeleton</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
@@ -1789,16 +1289,6 @@
           <t>混混：每次移动到格1时对玩家造成2点伤害</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>visual.face.monster.hoodlum</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.hoodlum</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -1816,16 +1306,6 @@
           <t>杀手：移动到玩家相邻格时强制战斗</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>visual.face.monster.killer</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.killer</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -1843,16 +1323,6 @@
           <t>巨石人：每次移动吸取相邻怪物全部护甲；累计损失10护甲洗入石人</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>visual.face.monster.megalith</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.megalith</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
@@ -1870,16 +1340,6 @@
           <t>迷雾：每移动1次攻击+2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>visual.face.monster.mist</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.mist</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -1897,16 +1357,6 @@
           <t>多骨虫：移动时与相邻两张怪物合成为巨大骷髅</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>visual.face.monster.multi_bone_worm</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.multi_bone_worm</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -1924,16 +1374,6 @@
           <t>观察者：怪物卡因怪物技能位移时伤害玩家</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>visual.face.monster.observer</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.observer</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -1951,16 +1391,6 @@
           <t>年迈兽人：战斗时恢复1且攻击+1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>visual.face.monster.old_orc</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.old_orc</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -1978,16 +1408,6 @@
           <t>兽人老大：每移动2次，移除相邻格子上的怪物卡和帮助卡；依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>visual.face.monster.orc_boss</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.orc_boss</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -2005,16 +1425,6 @@
           <t>兽人指挥官：每移动1次，相邻怪物攻击+1</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>visual.face.monster.orc_commander</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.orc_commander</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
@@ -2032,16 +1442,6 @@
           <t>兽人军需官：每移动2次随机强化其他怪物</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>visual.face.monster.orc_quartermaster</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.orc_quartermaster</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
@@ -2059,16 +1459,6 @@
           <t>兽人战士：战斗时每造成2点伤害，本卡攻击+1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>visual.face.monster.orc_warrior</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.orc_warrior</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -2086,16 +1476,6 @@
           <t>扒手：每移动3次移除相邻帮助卡</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>visual.face.monster.pickpocket</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.pickpocket</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
@@ -2113,16 +1493,6 @@
           <t>领头人：每移动3次创建福地，怪物进入福地获得护甲和攻击；福地达到3后下一次移动造成99伤害</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>visual.face.monster.ringleader</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.ringleader</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
@@ -2140,16 +1510,6 @@
           <t>流氓：每损失3点护甲，相邻怪物攻击+1</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>visual.face.monster.rogue</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.rogue</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -2167,16 +1527,6 @@
           <t>滚石人：移动到格3时移除格6帮助卡</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>visual.face.monster.rolling_stone_man</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.rolling_stone_man</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
@@ -2194,16 +1544,6 @@
           <t>旋转幼崽：每移动3次旋转</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>visual.face.monster.rotating_cub</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.rotating_cub</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
@@ -2221,16 +1561,6 @@
           <t>火蜥蜴：每移动3次放烈焰</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>visual.face.monster.salamander</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.salamander</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
@@ -2248,16 +1578,6 @@
           <t>尖石：护甲归零时伤害玩家</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>visual.face.monster.sharp_stone</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.sharp_stone</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
@@ -2275,16 +1595,6 @@
           <t>庇护石：其他怪物卡受到的伤害减少1点</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>visual.face.monster.shelter_stone</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.shelter_stone</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
@@ -2302,16 +1612,6 @@
           <t>骷髅王：相邻怪物被移除时获得其移除前攻击和护甲；每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>visual.face.monster.skeleton_king</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.skeleton_king</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
@@ -2329,16 +1629,6 @@
           <t>骷髅法师：所有怪物卡视为与本卡正交相邻</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>visual.face.monster.skeleton_mage</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.skeleton_mage</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -2356,16 +1646,6 @@
           <t>骷髅嘲讽子：相邻时只能与本卡战斗</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>visual.face.monster.skeleton_taunter</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.skeleton_taunter</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
@@ -2383,16 +1663,6 @@
           <t>骷髅头：相邻无头骷髅组合</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>visual.face.monster.skull_head</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.skull_head</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
@@ -2410,16 +1680,6 @@
           <t>空中巨眼：移动到角格时对玩家造成2点伤害</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>visual.face.monster.sky_eye</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.sky_eye</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
@@ -2437,16 +1697,6 @@
           <t>聪明兽人：每次获得攻击时，本卡额外攻击+1且不递归</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>visual.face.monster.smart_orc</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.smart_orc</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -2464,16 +1714,6 @@
           <t>走私者：累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>visual.face.monster.smuggler</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.smuggler</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
@@ -2491,16 +1731,6 @@
           <t>空间大师：玩家与本卡战斗后旋转一次；每移动9次从其他怪物牌组加入普通怪物</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>visual.face.monster.space_master</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.space_master</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -2518,16 +1748,6 @@
           <t>踏步行者：每移动3次与随机帮助卡交换</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>visual.face.monster.stepwalker</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.stepwalker</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -2545,16 +1765,6 @@
           <t>石傀儡</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>visual.face.monster.stone_golem</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.stone_golem</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
@@ -2572,16 +1782,6 @@
           <t>石头人</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>visual.face.monster.stone_man</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.stone_man</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
@@ -2599,16 +1799,6 @@
           <t>石虾：玩家卡和怪物卡损失护甲时本卡攻击+1</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>visual.face.monster.stone_shrimp</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.stone_shrimp</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
@@ -2626,16 +1816,6 @@
           <t>吞石者：每移动2次吸相邻怪物护甲</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>visual.face.monster.stone_swallower</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.stone_swallower</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
@@ -2653,16 +1833,6 @@
           <t>丢石人：每移动2次消耗本卡2护甲并伤害玩家</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>visual.face.monster.stone_thrower</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.stone_thrower</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
@@ -2680,16 +1850,6 @@
           <t>打手：登场在偶数边位时伤害玩家</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>visual.face.monster.thug</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.thug</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
@@ -2707,16 +1867,6 @@
           <t>流浪汉</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>visual.face.monster.vagrant</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.vagrant</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
@@ -2734,16 +1884,6 @@
           <t>历战兽人</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>visual.face.monster.veteran_orc</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.veteran_orc</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
@@ -2761,16 +1901,6 @@
           <t>虚空幼崽：每移动3次随机交换怪物</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>visual.face.monster.void_cub</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.void_cub</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
@@ -2788,16 +1918,6 @@
           <t>误入虚空者</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>visual.face.monster.void_lost</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.void_lost</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
@@ -2815,16 +1935,6 @@
           <t>流浪孩童：格6攻击+2并获得先攻</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>visual.face.monster.wandering_child</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.wandering_child</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
@@ -2842,16 +1952,6 @@
           <t>转动世界的手：登场旋转一次</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>visual.face.monster.world_turning_hand</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.world_turning_hand</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="B90" t="inlineStr">
@@ -2869,16 +1969,6 @@
           <t>年轻兽人：其他怪物获得攻击时本卡攻击+1</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>visual.face.monster.young_orc</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>visual.icon.monster.young_orc</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
@@ -2896,16 +1986,6 @@
           <t>巨龙牌组</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>visual.face.deck.dragon</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_42</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
@@ -2923,11 +2003,6 @@
           <t>兽人军团牌组</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>visual.face.deck.orc_legion</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
@@ -2945,11 +2020,6 @@
           <t>骷髅军团牌组</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>visual.face.deck.skeleton_legion</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
@@ -2967,11 +2037,6 @@
           <t>石人军团牌组</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>visual.face.deck.stone_legion</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
@@ -2989,11 +2054,6 @@
           <t>虚空牌组</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>visual.face.deck.void</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
@@ -3011,11 +2071,6 @@
           <t>流浪军团牌组</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>visual.face.deck.wandering_legion</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
@@ -3033,16 +2088,6 @@
           <t>渴望：所有恢复血量效果翻倍</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>visual.face.relic.craving</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.craving</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
@@ -3060,16 +2105,6 @@
           <t>龙鳞甲：所有怪物攻击-1</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>visual.face.relic.dragon_scale_armor</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.dragon_scale_armor</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
@@ -3087,16 +2122,6 @@
           <t>金币盔甲：金币抵消护甲伤害</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>visual.face.relic.gold_armor</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.gold_armor</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
@@ -3114,16 +2139,6 @@
           <t>打金刀：击杀怪物时获得2金币</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>visual.face.relic.gold_knife</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.gold_knife</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
@@ -3141,16 +2156,6 @@
           <t>重盔甲：基础护甲+1，按基础护甲补当前护甲</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>visual.face.relic.heavy_armor</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.heavy_armor</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
@@ -3168,16 +2173,6 @@
           <t>废物涂层：使用帮助卡时获得护甲</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>visual.face.relic.junk_coating</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.junk_coating</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
@@ -3195,16 +2190,6 @@
           <t>废物发射器：使用帮助卡时随机伤害</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>visual.face.relic.junk_launcher</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.junk_launcher</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
@@ -3222,16 +2207,6 @@
           <t>废物利用机：使用帮助卡时恢复2点血量</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>visual.face.relic.junk_recycler</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.junk_recycler</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
@@ -3249,16 +2224,6 @@
           <t>废物老虎机：使用帮助卡时随机触发九选一</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>visual.face.relic.junk_slot_machine</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.junk_slot_machine</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
@@ -3276,16 +2241,6 @@
           <t>幸运硬币：击杀精英/层主时加入金币卡</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>visual.face.relic.lucky_coin</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.lucky_coin</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
@@ -3303,16 +2258,6 @@
           <t>凤凰羽毛：致命伤害免死</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>visual.face.relic.phoenix_feather</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.phoenix_feather</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
@@ -3330,16 +2275,6 @@
           <t>药水袋：每关卡开始加入两张恢复药水</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>visual.face.relic.potion_bag</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.potion_bag</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
@@ -3357,16 +2292,6 @@
           <t>打盾刀：击杀怪物时获得护甲</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>visual.face.relic.shield_knife</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.shield_knife</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
@@ -3384,16 +2309,6 @@
           <t>弹弓：击杀怪物时随机伤害</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>visual.face.relic.sling</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.sling</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
@@ -3411,16 +2326,6 @@
           <t>飞刀袋：每关卡开始加入两张飞刀</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>visual.face.relic.throwing_knife_bag</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.throwing_knife_bag</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
@@ -3438,16 +2343,6 @@
           <t>活力护符：血量上限+6，关卡结束恢复6</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>visual.face.relic.vitality_amulet</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.vitality_amulet</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
@@ -3465,16 +2360,6 @@
           <t>木甲：血量上限+2，木套装额外+8</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>visual.face.relic.wood_armor</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.wood_armor</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
@@ -3492,16 +2377,6 @@
           <t>木盾：基础护甲+1，木套装额外+2</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>visual.face.relic.wood_shield</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.wood_shield</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
@@ -3519,16 +2394,6 @@
           <t>木剑：攻击+1，木套装额外+2</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>visual.face.relic.wood_sword</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>visual.icon.relic.wood_sword</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="B116" t="inlineStr">
@@ -3546,11 +2411,6 @@
           <t>温泉房</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>visual.icon.Fountain</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
@@ -3568,11 +2428,6 @@
           <t>金币房</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>visual.icon.Gold</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
@@ -3590,11 +2445,6 @@
           <t>商店</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>visual.icon.Shop</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
@@ -3612,11 +2462,6 @@
           <t>酒馆</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>visual.icon.Tavern</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
@@ -3634,11 +2479,6 @@
           <t>宝箱房</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>visual.icon.Treasure</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
@@ -3656,16 +2496,6 @@
           <t>吸骨：相邻怪物被移除时获得其移除前攻击和护甲</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>visual.face.skill.absorb_bone</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.absorb_bone</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
@@ -3683,16 +2513,6 @@
           <t>吸石：每次移动吸取相邻怪物全部护甲</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>visual.face.skill.absorb_stone</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.absorb_stone</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
@@ -3710,16 +2530,6 @@
           <t>空中打击：移动到角格时对玩家造成2点伤害</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>visual.face.skill.air_strike</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.air_strike</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
@@ -3737,16 +2547,6 @@
           <t>军械库：关卡结束加入飞刀/爆弹/破击锤之一</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>visual.face.skill.arsenal</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.arsenal</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
@@ -3764,16 +2564,6 @@
           <t>历战：战斗时攻击+2，换敌复原</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>visual.face.skill.battle_hardened</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.battle_hardened</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
@@ -3791,16 +2581,6 @@
           <t>丐帮同心：每移动5次洗入乞丐</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>visual.face.skill.beggar_bond</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.beggar_bond</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
@@ -3818,16 +2598,6 @@
           <t>庇佑：下一次受到伤害时，该次伤害变为0</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>visual.face.skill.blessing</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.blessing</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="B128" t="inlineStr">
@@ -3845,16 +2615,6 @@
           <t>嗜血：战斗时每造成2点伤害，本卡攻击+1</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>visual.face.skill.bloodthirst</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.bloodthirst</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
@@ -3872,16 +2632,6 @@
           <t>喷火：每移动3次放烈焰</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>visual.face.skill.breathe_fire</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.breathe_fire</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="B130" t="inlineStr">
@@ -3899,16 +2649,6 @@
           <t>呼唤信徒：每移动3次加入龙信徒</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>visual.face.skill.call_followers</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.call_followers</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
@@ -3926,16 +2666,6 @@
           <t>快递：每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>visual.face.skill.delivery</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.delivery</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
@@ -3953,16 +2683,6 @@
           <t>献身：被移除时加入烈焰</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>visual.face.skill.devotion</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.devotion</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="B133" t="inlineStr">
@@ -3980,16 +2700,6 @@
           <t>轻车熟路：关卡结束白色帮助卡三选一</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>visual.face.skill.easy_road</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.easy_road</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="B134" t="inlineStr">
@@ -4007,16 +2717,6 @@
           <t>偶数仇恨：对偶数等级怪物造成双倍伤害</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>visual.face.skill.even_hatred</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.even_hatred</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="B135" t="inlineStr">
@@ -4034,16 +2734,6 @@
           <t>散架：被移除时洗入骷髅头与无头骷髅</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>visual.face.skill.fall_apart</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.fall_apart</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="B136" t="inlineStr">
@@ -4061,16 +2751,6 @@
           <t>落石：累计损失10护甲洗入石人</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>visual.face.skill.falling_rocks</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.falling_rocks</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="B137" t="inlineStr">
@@ -4088,16 +2768,6 @@
           <t>和我打！：相邻玩家与其他怪物战斗时改为与本卡战斗</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>visual.face.skill.fight_me</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.fight_me</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
@@ -4115,16 +2785,6 @@
           <t>发现弱点：福地达到3后下一次移动造成99伤害</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>visual.face.skill.find_weakness</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.find_weakness</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="B139" t="inlineStr">
@@ -4142,16 +2802,6 @@
           <t>火之力：每有一张烈焰，本卡攻击+2</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>visual.face.skill.fire_power</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.fire_power</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="B140" t="inlineStr">
@@ -4169,16 +2819,6 @@
           <t>先攻：持有先攻技能</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>visual.face.skill.first_strike</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.first_strike</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="B141" t="inlineStr">
@@ -4196,16 +2836,6 @@
           <t>烈焰沸腾：烈焰帮助卡造成的伤害+1</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>visual.face.skill.flame_boiling</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.flame_boiling</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
@@ -4223,16 +2853,6 @@
           <t>烈焰吐息：每移动4次移除其他普通怪物并按数量加入烈焰</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>visual.face.skill.flame_breath</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.flame_breath</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="B143" t="inlineStr">
@@ -4250,16 +2870,6 @@
           <t>折损散架：被移除时洗入多骨虫和等级2随机怪物</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>visual.face.skill.fracture_fall_apart</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.fracture_fall_apart</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="B144" t="inlineStr">
@@ -4277,16 +2887,6 @@
           <t>发装备了！：每移动2次随机强化其他怪物</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>visual.face.skill.gear_delivery</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.gear_delivery</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="B145" t="inlineStr">
@@ -4304,16 +2904,6 @@
           <t>礼物：每移动3次放旋转轮</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>visual.face.skill.gift</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.gift</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="B146" t="inlineStr">
@@ -4331,16 +2921,6 @@
           <t>给你一拳：登场在偶数边位时伤害玩家</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>visual.face.skill.give_punch</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.give_punch</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="B147" t="inlineStr">
@@ -4358,16 +2938,6 @@
           <t>引路：每移动3次创建福地，怪物进入福地获得护甲和攻击</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>visual.face.skill.guide</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.guide</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="B148" t="inlineStr">
@@ -4385,16 +2955,6 @@
           <t>坚硬：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>visual.face.skill.hard</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.hard</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="B149" t="inlineStr">
@@ -4412,16 +2972,6 @@
           <t>硬皮：血量上限+10，关卡结束恢复10</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>visual.face.skill.hard_skin</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.hard_skin</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="B150" t="inlineStr">
@@ -4439,16 +2989,6 @@
           <t>混的人：每次移动到格1时对玩家造成2点伤害</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>visual.face.skill.hoodlum</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.hoodlum</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
@@ -4466,16 +3006,6 @@
           <t>灼热观察：怪物卡因怪物技能位移时伤害玩家</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>visual.face.skill.hot_observation</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.hot_observation</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="B152" t="inlineStr">
@@ -4493,16 +3023,6 @@
           <t>剧烈燃烧：每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>visual.face.skill.intense_burning</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.intense_burning</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="B153" t="inlineStr">
@@ -4520,16 +3040,6 @@
           <t>学习成长：其他怪物获得攻击时本卡攻击+1</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>visual.face.skill.learning_growth</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.learning_growth</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="B154" t="inlineStr">
@@ -4547,16 +3057,6 @@
           <t>恋火：有烈焰时攻击+4</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>visual.face.skill.love_fire</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.love_fire</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
@@ -4574,16 +3074,6 @@
           <t>混合骨头：每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>visual.face.skill.mixed_bones</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.mixed_bones</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="B156" t="inlineStr">
@@ -4601,16 +3091,6 @@
           <t>历战怪物：战斗时本卡攻击+2</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>visual.face.skill.monster_battle_hardened</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.monster_battle_hardened</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="B157" t="inlineStr">
@@ -4628,16 +3108,6 @@
           <t>兽人战术：每移动1次，相邻怪物攻击+1</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>visual.face.skill.orc_tactics</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.orc_tactics</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="B158" t="inlineStr">
@@ -4655,16 +3125,6 @@
           <t>异界帮助：每移动9次从其他怪物牌组加入普通怪物</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>visual.face.skill.otherworld_help</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.otherworld_help</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="B159" t="inlineStr">
@@ -4682,16 +3142,6 @@
           <t>乱步：每移动3次与随机帮助卡交换</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>visual.face.skill.random_walk</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.random_walk</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="B160" t="inlineStr">
@@ -4709,16 +3159,6 @@
           <t>范围扩大：所有怪物卡视为与本卡正交相邻</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>visual.face.skill.range_expand</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.range_expand</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="B161" t="inlineStr">
@@ -4736,16 +3176,6 @@
           <t>痞气：每损失3点护甲，相邻怪物攻击+1</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>visual.face.skill.rascality</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.rascality</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="B162" t="inlineStr">
@@ -4763,16 +3193,6 @@
           <t>重新组合身：相邻无头骷髅组合</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>visual.face.skill.recombine_body</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.recombine_body</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="B163" t="inlineStr">
@@ -4790,16 +3210,6 @@
           <t>重新组合头：相邻骷髅头组合</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>visual.face.skill.recombine_head</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.recombine_head</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="B164" t="inlineStr">
@@ -4817,16 +3227,6 @@
           <t>不休追击：移动到玩家相邻格时强制战斗</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>visual.face.skill.relentless_chase</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.relentless_chase</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="B165" t="inlineStr">
@@ -4844,16 +3244,6 @@
           <t>滚动碾压：移动到格3时移除格6帮助卡</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>visual.face.skill.rolling_crush</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.rolling_crush</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="B166" t="inlineStr">
@@ -4871,16 +3261,6 @@
           <t>爱好旋转：每移动3次旋转</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>visual.face.skill.rotate_lover</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.rotate_lover</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="B167" t="inlineStr">
@@ -4898,16 +3278,6 @@
           <t>献祭：每移动2次，移除九宫格上所有的龙信徒</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>visual.face.skill.sacrifice</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.sacrifice</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="B168" t="inlineStr">
@@ -4925,16 +3295,6 @@
           <t>尖石：护甲归零时伤害玩家</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>visual.face.skill.sharp_stone</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.sharp_stone</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="B169" t="inlineStr">
@@ -4952,16 +3312,6 @@
           <t>大聪明：每次获得攻击时，本卡额外攻击+1且不递归</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>visual.face.skill.smart</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.smart</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="B170" t="inlineStr">
@@ -4979,16 +3329,6 @@
           <t>空间掌握：玩家与本卡战斗后旋转一次</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>visual.face.skill.space_mastery</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.space_mastery</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="B171" t="inlineStr">
@@ -5006,16 +3346,6 @@
           <t>进货：累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>visual.face.skill.stocking</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.stocking</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="B172" t="inlineStr">
@@ -5033,16 +3363,6 @@
           <t>石增长：移动到左列时其他怪物获得2点护甲</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>visual.face.skill.stone_growth</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.stone_growth</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="B173" t="inlineStr">
@@ -5060,16 +3380,6 @@
           <t>石头爱好者：玩家卡和怪物卡损失护甲时本卡攻击+1</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>visual.face.skill.stone_lover</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.stone_lover</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="B174" t="inlineStr">
@@ -5087,16 +3397,6 @@
           <t>石庇护：其他怪物卡受到的伤害减少1点</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>visual.face.skill.stone_shelter</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.stone_shelter</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="B175" t="inlineStr">
@@ -5114,16 +3414,6 @@
           <t>流浪幼崽：格6攻击+2并获得先攻</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>visual.face.skill.stray_cub</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.stray_cub</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="B176" t="inlineStr">
@@ -5141,16 +3431,6 @@
           <t>漫步：每移动1次攻击+2</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>visual.face.skill.stroll</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.stroll</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="B177" t="inlineStr">
@@ -5168,16 +3448,6 @@
           <t>强力组合：移动时与相邻两张怪物合成为巨大骷髅</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>visual.face.skill.strong_combo</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.strong_combo</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="B178" t="inlineStr">
@@ -5195,16 +3465,6 @@
           <t>生存智慧：战斗时恢复1且攻击+1</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>visual.face.skill.survival_wisdom</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.survival_wisdom</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="B179" t="inlineStr">
@@ -5222,16 +3482,6 @@
           <t>吞石：每移动2次吸相邻怪物护甲</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>visual.face.skill.swallow_stone</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.swallow_stone</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="B180" t="inlineStr">
@@ -5249,16 +3499,6 @@
           <t>嘲讽：相邻时只能与本卡战斗</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>visual.face.skill.taunt</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.taunt</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="B181" t="inlineStr">
@@ -5276,16 +3516,6 @@
           <t>东西归我了！：每移动3次移除相邻帮助卡</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>visual.face.skill.thief_claims</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.thief_claims</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="B182" t="inlineStr">
@@ -5303,16 +3533,6 @@
           <t>刺皮：战斗时对怪物造成等同其攻击的伤害</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>visual.face.skill.thorn_skin</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.thorn_skin</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="B183" t="inlineStr">
@@ -5330,16 +3550,6 @@
           <t>丢石头：每移动2次消耗本卡2护甲并伤害玩家</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>visual.face.skill.throw_stone</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.throw_stone</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="B184" t="inlineStr">
@@ -5357,16 +3567,6 @@
           <t>塔之子：关卡开始放入倍增塔</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>visual.face.skill.tower_child</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.tower_child</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="B185" t="inlineStr">
@@ -5384,16 +3584,6 @@
           <t>转动：登场旋转一次</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>visual.face.skill.turn_world</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.turn_world</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="B186" t="inlineStr">
@@ -5411,16 +3601,6 @@
           <t>不稳定：每移动3次随机交换怪物</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>visual.face.skill.unstable</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.unstable</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="B187" t="inlineStr">
@@ -5438,16 +3618,6 @@
           <t>暴力狂：每移动2次，移除相邻格子上的怪物卡和帮助卡</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>visual.face.skill.violence_maniac</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.violence_maniac</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="B188" t="inlineStr">
@@ -5463,16 +3633,6 @@
       <c r="D188" t="inlineStr">
         <is>
           <t>暴力即养分：依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>visual.face.skill.violence_nutrition</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>visual.icon.skill.violence_nutrition</t>
         </is>
       </c>
     </row>

--- a/Assets/Tools/Luban/Datas/content_visual.xlsx
+++ b/Assets/Tools/Luban/Datas/content_visual.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D188"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="37.44140625" customWidth="1" min="2" max="2"/>
@@ -3636,6 +3636,57 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ChoiceOption</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>攻击+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ChoiceOption</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>护甲+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Hp</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ChoiceOption</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>血量上限与当前血量+2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Tools/Luban/Datas/content_visual.xlsx
+++ b/Assets/Tools/Luban/Datas/content_visual.xlsx
@@ -1,34 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TbContentVisual" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -56,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,16 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="37.44140625" customWidth="1" min="2" max="2"/>
-    <col width="11.21875" customWidth="1" min="3" max="3"/>
-    <col width="172.109375" customWidth="1" min="4" max="4"/>
-    <col width="24.21875" customWidth="1" min="5" max="5"/>
-    <col width="11.109375" customWidth="1" min="6" max="6"/>
-    <col width="9.77734375" customWidth="1" min="7" max="7"/>
-  </cols>
+  <dimension ref="A1:D192"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -475,6 +461,7 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>avatar.default</t>
@@ -492,6 +479,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>help.armor_breaking_hammer</t>
@@ -509,6 +497,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>help.bear_trap</t>
@@ -526,6 +515,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>help.blood_conversion</t>
@@ -543,6 +533,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>help.blue_chest_card</t>
@@ -560,6 +551,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>help.bomb</t>
@@ -577,6 +569,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>help.brutality_card</t>
@@ -594,6 +587,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>help.common_chest_card</t>
@@ -611,6 +605,7 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>help.doubling_tower</t>
@@ -628,6 +623,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>help.fireball</t>
@@ -645,6 +641,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>help.flame</t>
@@ -662,6 +659,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>help.food_card</t>
@@ -679,6 +677,7 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>help.gold_card</t>
@@ -696,6 +695,7 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>help.golden_chest_card</t>
@@ -713,6 +713,7 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>help.healing_potion</t>
@@ -730,6 +731,7 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>help.healing_spring</t>
@@ -747,6 +749,7 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>help.impact_tutorial</t>
@@ -764,6 +767,7 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>help.kidnapping</t>
@@ -781,6 +785,7 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>help.rolling_stone</t>
@@ -798,6 +803,7 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>help.rotation_wheel</t>
@@ -815,6 +821,7 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>help.shield_bash_tutorial</t>
@@ -832,6 +839,7 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>help.stat_boost_card</t>
@@ -849,6 +857,7 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>help.sturdy_shield</t>
@@ -866,6 +875,7 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>help.swap_card</t>
@@ -883,6 +893,7 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>help.teleport_card</t>
@@ -900,6 +911,7 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>help.throwing_knife</t>
@@ -917,6 +929,7 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>help.ward_magic_card</t>
@@ -934,6 +947,7 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>help.watchtower</t>
@@ -951,6 +965,7 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>monster.beggar</t>
@@ -968,6 +983,7 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>monster.big_orc</t>
@@ -985,6 +1001,7 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>monster.big_skeleton</t>
@@ -1002,2688 +1019,2864 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
+          <t>monster.big_skeleton_reborn</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>重组大骷髅</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>monster.big_stone</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>大石头：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
         <is>
           <t>monster.bone_club_skeleton</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>骨棒骷髅</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
         <is>
           <t>monster.bone_courier</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>骨头快递员：每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
         <is>
           <t>monster.brainless_orc</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>无脑兽人：战斗时本卡攻击+2</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
         <is>
           <t>monster.dragon_cult_leader</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>龙教主：每移动3次加入龙信徒</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
         <is>
           <t>monster.dragon_follower</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>龙信徒：被移除时加入烈焰</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
         <is>
           <t>monster.executioner</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>刽子手：每移动2次，移除九宫格上所有的龙信徒</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
         <is>
           <t>monster.fire_bather</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>浴火者：有烈焰时攻击+4</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
         <is>
           <t>monster.fire_cult_leader</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>火教主：每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
         <is>
           <t>monster.fire_dragon</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>火龙：每移动4次移除其他普通怪物并按数量加入烈焰；烈焰帮助卡造成的伤害+1</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
         <is>
           <t>monster.fire_priest</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>火焰祭司：每有一张烈焰，本卡攻击+2</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
         <is>
           <t>monster.fire_swallower</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>吞火者：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
         <is>
           <t>monster.friendly_ancient</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>友好的远古生物：每移动3次放旋转轮</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
         <is>
           <t>monster.giant_skeleton</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>巨大骷髅：被移除时洗入多骨虫和等级2随机怪物</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
         <is>
           <t>monster.growing_stone</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>增生石块：移动到左列时其他怪物获得2点护甲</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
         <is>
           <t>monster.headless_skeleton</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>无头骷髅：相邻骷髅头组合</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
         <is>
           <t>monster.hoodlum</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>混混：每次移动到格1时对玩家造成2点伤害</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
         <is>
           <t>monster.killer</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>杀手：移动到玩家相邻格时强制战斗</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>monster.megalith</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>巨石人：每次移动吸取相邻怪物全部护甲；累计损失10护甲洗入石人</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
         <is>
           <t>monster.mist</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>迷雾：每移动1次攻击+2</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
         <is>
           <t>monster.multi_bone_worm</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>多骨虫：移动时与相邻两张怪物合成为巨大骷髅</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
         <is>
           <t>monster.observer</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>观察者：怪物卡因怪物技能位移时伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
         <is>
           <t>monster.old_orc</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>年迈兽人：战斗时恢复1且攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
         <is>
           <t>monster.orc_boss</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>兽人老大：每移动2次，移除相邻格子上的怪物卡和帮助卡；依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
         <is>
           <t>monster.orc_commander</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>兽人指挥官：每移动1次，相邻怪物攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
         <is>
           <t>monster.orc_quartermaster</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>兽人军需官：每移动2次随机强化其他怪物</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
         <is>
           <t>monster.orc_warrior</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>兽人战士：战斗时每造成2点伤害，本卡攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>monster.pickpocket</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>扒手：每移动3次移除相邻帮助卡</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
         <is>
           <t>monster.ringleader</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>领头人：每移动3次创建福地，怪物进入福地获得护甲和攻击；福地达到3后下一次移动造成99伤害</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
         <is>
           <t>monster.rogue</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>流氓：每损失3点护甲，相邻怪物攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
         <is>
           <t>monster.rolling_stone_man</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>滚石人：移动到格3时移除格6帮助卡</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
         <is>
           <t>monster.rotating_cub</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>旋转幼崽：每移动3次旋转</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
         <is>
           <t>monster.salamander</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>火蜥蜴：每移动3次放烈焰</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
         <is>
           <t>monster.sharp_stone</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>尖石：护甲归零时伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
         <is>
           <t>monster.shelter_stone</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>庇护石：其他怪物卡受到的伤害减少1点</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
         <is>
           <t>monster.skeleton_king</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>骷髅王：相邻怪物被移除时获得其移除前攻击和护甲；每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
         <is>
           <t>monster.skeleton_mage</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>骷髅法师：所有怪物卡视为与本卡正交相邻</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
         <is>
           <t>monster.skeleton_taunter</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>骷髅嘲讽子：相邻时只能与本卡战斗</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
         <is>
           <t>monster.skull_head</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>骷髅头：相邻无头骷髅组合</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
         <is>
           <t>monster.sky_eye</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>空中巨眼：移动到角格时对玩家造成2点伤害</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
         <is>
           <t>monster.smart_orc</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>聪明兽人：每次获得攻击时，本卡额外攻击+1且不递归</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
         <is>
           <t>monster.smuggler</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>走私者：累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
         <is>
           <t>monster.space_master</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>空间大师：玩家与本卡战斗后旋转一次；每移动9次从其他怪物牌组加入普通怪物</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
         <is>
           <t>monster.stepwalker</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>踏步行者：每移动3次与随机帮助卡交换</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
         <is>
           <t>monster.stone_golem</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>石傀儡</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
         <is>
           <t>monster.stone_man</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>石头人</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
         <is>
           <t>monster.stone_shrimp</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>石虾：玩家卡和怪物卡损失护甲时本卡攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
         <is>
           <t>monster.stone_swallower</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>吞石者：每移动2次吸相邻怪物护甲</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
         <is>
           <t>monster.stone_thrower</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>丢石人：每移动2次消耗本卡2护甲并伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
         <is>
           <t>monster.thug</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>打手：登场在偶数边位时伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
         <is>
           <t>monster.vagrant</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>流浪汉</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
         <is>
           <t>monster.veteran_orc</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>历战兽人</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
         <is>
           <t>monster.void_cub</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>虚空幼崽：每移动3次随机交换怪物</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
         <is>
           <t>monster.void_lost</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>误入虚空者</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
         <is>
           <t>monster.wandering_child</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>流浪孩童：格6攻击+2并获得先攻</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
         <is>
           <t>monster.world_turning_hand</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>转动世界的手：登场旋转一次</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
         <is>
           <t>monster.young_orc</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Monster</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>年轻兽人：其他怪物获得攻击时本卡攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
         <is>
           <t>deck.dragon</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>MonsterDeck</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>巨龙牌组</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
         <is>
           <t>deck.orc_legion</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>MonsterDeck</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>兽人军团牌组</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
         <is>
           <t>deck.skeleton_legion</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>MonsterDeck</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>骷髅军团牌组</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
         <is>
           <t>deck.stone_legion</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>MonsterDeck</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>石人军团牌组</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
         <is>
           <t>deck.void</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>MonsterDeck</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>虚空牌组</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
         <is>
           <t>deck.wandering_legion</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>MonsterDeck</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>流浪军团牌组</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>relic.blood_shockwave</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>血液冲击波：血量上限+4，关卡开始放入撞击教程，低血再放一张</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
         <is>
           <t>relic.craving</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>渴望：所有恢复血量效果翻倍</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
         <is>
           <t>relic.dragon_scale_armor</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>龙鳞甲：所有怪物攻击-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" t="inlineStr">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>龙鳞甲：基础护甲+1，血量上限+6，怪物攻击-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
         <is>
           <t>relic.gold_armor</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>金币盔甲：金币抵消护甲伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" t="inlineStr">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>金币盔甲：基础护甲+1，金币抵消护甲伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
         <is>
           <t>relic.gold_knife</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>打金刀：击杀怪物时获得2金币</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
         <is>
           <t>relic.heavy_armor</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>重盔甲：基础护甲+1，按基础护甲补当前护甲</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
         <is>
           <t>relic.junk_coating</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>废物涂层：使用帮助卡时获得护甲</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
         <is>
           <t>relic.junk_launcher</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>废物发射器：使用帮助卡时随机伤害</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
         <is>
           <t>relic.junk_recycler</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>废物利用机：使用帮助卡时恢复2点血量</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
         <is>
           <t>relic.junk_slot_machine</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>废物老虎机：使用帮助卡时随机触发九选一</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
         <is>
           <t>relic.lucky_coin</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>幸运硬币：击杀精英/层主时加入金币卡</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
         <is>
           <t>relic.phoenix_feather</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>凤凰羽毛：致命伤害免死</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" t="inlineStr">
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>凤凰羽毛：血量上限+8，致命伤害免死</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
         <is>
           <t>relic.potion_bag</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>药水袋：每关卡开始加入两张恢复药水</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>relic.rotation_button</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>旋转按钮：每关卡开始放入旋转轮</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
         <is>
           <t>relic.shield_knife</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>打盾刀：击杀怪物时获得护甲</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
         <is>
           <t>relic.sling</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>弹弓：击杀怪物时随机伤害</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>relic.swap_button</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>交换按钮：每关卡开始放入交换卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
         <is>
           <t>relic.throwing_knife_bag</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>飞刀袋：每关卡开始加入两张飞刀</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
         <is>
           <t>relic.vitality_amulet</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>活力护符：血量上限+6，关卡结束恢复6</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
         <is>
           <t>relic.wood_armor</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>木甲：血量上限+2，木套装额外+8</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="B114" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
         <is>
           <t>relic.wood_shield</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>木盾：基础护甲+1，木套装额外+2</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="B115" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
         <is>
           <t>relic.wood_sword</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Relic</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>木剑：攻击+1，木套装额外+2</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="B116" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
         <is>
           <t>Fountain</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>温泉房</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="B117" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>金币房</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="B118" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>商店</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="B119" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
         <is>
           <t>Tavern</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>酒馆</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
         <is>
           <t>Treasure</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>宝箱房</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
         <is>
           <t>skill.absorb_bone</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>吸骨：相邻怪物被移除时获得其移除前攻击和护甲</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
         <is>
           <t>skill.absorb_stone</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
         <is>
           <t>吸石：每次移动吸取相邻怪物全部护甲</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="B123" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
         <is>
           <t>skill.air_strike</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
         <is>
           <t>空中打击：移动到角格时对玩家造成2点伤害</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="B124" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
         <is>
           <t>skill.arsenal</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>军械库：关卡结束加入飞刀/爆弹/破击锤之一</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="B125" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
         <is>
           <t>skill.battle_hardened</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
         <is>
           <t>历战：战斗时攻击+2，换敌复原</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
         <is>
           <t>skill.beggar_bond</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
         <is>
           <t>丐帮同心：每移动5次洗入乞丐</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="B127" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
         <is>
           <t>skill.blessing</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
         <is>
           <t>庇佑：下一次受到伤害时，该次伤害变为0</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="B128" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
         <is>
           <t>skill.bloodthirst</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
         <is>
           <t>嗜血：战斗时每造成2点伤害，本卡攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
         <is>
           <t>skill.breathe_fire</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
         <is>
           <t>喷火：每移动3次放烈焰</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="B130" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
         <is>
           <t>skill.call_followers</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
         <is>
           <t>呼唤信徒：每移动3次加入龙信徒</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="B131" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
         <is>
           <t>skill.delivery</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
         <is>
           <t>快递：每移动2次，将相邻帮助卡与战斗卡组怪物交换</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="B132" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
         <is>
           <t>skill.devotion</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>献身：被移除时加入烈焰</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="B133" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
         <is>
           <t>skill.easy_road</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t>轻车熟路：关卡结束白色帮助卡三选一</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="B134" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
         <is>
           <t>skill.even_hatred</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
         <is>
           <t>偶数仇恨：对偶数等级怪物造成双倍伤害</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="B135" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
         <is>
           <t>skill.fall_apart</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
         <is>
           <t>散架：被移除时洗入骷髅头与无头骷髅</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="B136" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
         <is>
           <t>skill.falling_rocks</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
         <is>
           <t>落石：累计损失10护甲洗入石人</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="B137" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
         <is>
           <t>skill.fight_me</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
         <is>
           <t>和我打！：相邻玩家与其他怪物战斗时改为与本卡战斗</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="B138" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
         <is>
           <t>skill.find_weakness</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
         <is>
           <t>发现弱点：福地达到3后下一次移动造成99伤害</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
         <is>
           <t>skill.fire_power</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t>火之力：每有一张烈焰，本卡攻击+2</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="B140" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
         <is>
           <t>skill.first_strike</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
         <is>
           <t>先攻：持有先攻技能</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="B141" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
         <is>
           <t>skill.flame_boiling</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
         <is>
           <t>烈焰沸腾：烈焰帮助卡造成的伤害+1</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="B142" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
         <is>
           <t>skill.flame_breath</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
         <is>
           <t>烈焰吐息：每移动4次移除其他普通怪物并按数量加入烈焰</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="B143" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
         <is>
           <t>skill.fracture_fall_apart</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
         <is>
           <t>折损散架：被移除时洗入多骨虫和等级2随机怪物</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="B144" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
         <is>
           <t>skill.gear_delivery</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
         <is>
           <t>发装备了！：每移动2次随机强化其他怪物</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="B145" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
         <is>
           <t>skill.gift</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
         <is>
           <t>礼物：每移动3次放旋转轮</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="B146" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
         <is>
           <t>skill.give_punch</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
         <is>
           <t>给你一拳：登场在偶数边位时伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="B147" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
         <is>
           <t>skill.guide</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
         <is>
           <t>引路：每移动3次创建福地，怪物进入福地获得护甲和攻击</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="B148" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
         <is>
           <t>skill.hard</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
         <is>
           <t>坚硬：左列战斗时按损失护甲伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
         <is>
           <t>skill.hard_skin</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
         <is>
           <t>硬皮：血量上限+10，关卡结束恢复10</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="B150" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
         <is>
           <t>skill.hoodlum</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
         <is>
           <t>混的人：每次移动到格1时对玩家造成2点伤害</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="B151" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
         <is>
           <t>skill.hot_observation</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
         <is>
           <t>灼热观察：怪物卡因怪物技能位移时伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="B152" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
         <is>
           <t>skill.intense_burning</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
         <is>
           <t>剧烈燃烧：每有一张烈焰加入战斗卡组，额外加入一张且不递归</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="B153" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
         <is>
           <t>skill.learning_growth</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
         <is>
           <t>学习成长：其他怪物获得攻击时本卡攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
         <is>
           <t>skill.love_fire</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
         <is>
           <t>恋火：有烈焰时攻击+4</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="B155" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
         <is>
           <t>skill.mixed_bones</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
         <is>
           <t>混合骨头：每移动5次移除随机两张其他怪物并洗入等级2/3随机怪物</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="B156" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
         <is>
           <t>skill.monster_battle_hardened</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
         <is>
           <t>历战怪物：战斗时本卡攻击+2</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="B157" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
         <is>
           <t>skill.orc_tactics</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
         <is>
           <t>兽人战术：每移动1次，相邻怪物攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="B158" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
         <is>
           <t>skill.otherworld_help</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
         <is>
           <t>异界帮助：每移动9次从其他怪物牌组加入普通怪物</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="B159" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
         <is>
           <t>skill.random_walk</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
         <is>
           <t>乱步：每移动3次与随机帮助卡交换</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="B160" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
         <is>
           <t>skill.range_expand</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
         <is>
           <t>范围扩大：所有怪物卡视为与本卡正交相邻</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="B161" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
         <is>
           <t>skill.rascality</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
         <is>
           <t>痞气：每损失3点护甲，相邻怪物攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="B162" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
         <is>
           <t>skill.recombine_body</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
         <is>
           <t>重新组合身：相邻无头骷髅组合</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="B163" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
         <is>
           <t>skill.recombine_head</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
         <is>
           <t>重新组合头：相邻骷髅头组合</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="B164" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
         <is>
           <t>skill.relentless_chase</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
         <is>
           <t>不休追击：移动到玩家相邻格时强制战斗</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="B165" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
         <is>
           <t>skill.rolling_crush</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
         <is>
           <t>滚动碾压：移动到格3时移除格6帮助卡</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="B166" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
         <is>
           <t>skill.rotate_lover</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
         <is>
           <t>爱好旋转：每移动3次旋转</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="B167" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
         <is>
           <t>skill.sacrifice</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
         <is>
           <t>献祭：每移动2次，移除九宫格上所有的龙信徒</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="B168" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
         <is>
           <t>skill.sharp_stone</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
         <is>
           <t>尖石：护甲归零时伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="B169" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
         <is>
           <t>skill.smart</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
         <is>
           <t>大聪明：每次获得攻击时，本卡额外攻击+1且不递归</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="B170" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
         <is>
           <t>skill.space_mastery</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
         <is>
           <t>空间掌握：玩家与本卡战斗后旋转一次</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="B171" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
         <is>
           <t>skill.stocking</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
         <is>
           <t>进货：累计移动到玩家相邻3次时移除帮助卡并获得护甲</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="B172" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
         <is>
           <t>skill.stone_growth</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
         <is>
           <t>石增长：移动到左列时其他怪物获得2点护甲</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="B173" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
         <is>
           <t>skill.stone_lover</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
         <is>
           <t>石头爱好者：玩家卡和怪物卡损失护甲时本卡攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="B174" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
         <is>
           <t>skill.stone_shelter</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
         <is>
           <t>石庇护：其他怪物卡受到的伤害减少1点</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="B175" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
         <is>
           <t>skill.stray_cub</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
         <is>
           <t>流浪幼崽：格6攻击+2并获得先攻</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="B176" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
         <is>
           <t>skill.stroll</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
         <is>
           <t>漫步：每移动1次攻击+2</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="B177" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
         <is>
           <t>skill.strong_combo</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
         <is>
           <t>强力组合：移动时与相邻两张怪物合成为巨大骷髅</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="B178" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
         <is>
           <t>skill.survival_wisdom</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
         <is>
           <t>生存智慧：战斗时恢复1且攻击+1</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="B179" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
         <is>
           <t>skill.swallow_stone</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
         <is>
           <t>吞石：每移动2次吸相邻怪物护甲</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="B180" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
         <is>
           <t>skill.taunt</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
         <is>
           <t>嘲讽：相邻时只能与本卡战斗</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="B181" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
         <is>
           <t>skill.thief_claims</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
         <is>
           <t>东西归我了！：每移动3次移除相邻帮助卡</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="B182" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
         <is>
           <t>skill.thorn_skin</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
         <is>
           <t>刺皮：战斗时对怪物造成等同其攻击的伤害</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="B183" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
         <is>
           <t>skill.throw_stone</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
         <is>
           <t>丢石头：每移动2次消耗本卡2护甲并伤害玩家</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="B184" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
         <is>
           <t>skill.tower_child</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
         <is>
           <t>塔之子：关卡开始放入倍增塔</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="B185" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
         <is>
           <t>skill.turn_world</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
         <is>
           <t>转动：登场旋转一次</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="B186" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
         <is>
           <t>skill.unstable</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
         <is>
           <t>不稳定：每移动3次随机交换怪物</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="B187" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
         <is>
           <t>skill.violence_maniac</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
         <is>
           <t>暴力狂：每移动2次，移除相邻格子上的怪物卡和帮助卡</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="B188" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
         <is>
           <t>skill.violence_nutrition</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
         <is>
           <t>暴力即养分：依靠暴力狂移除怪物得攻击，移除帮助卡得护甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>ChoiceOption</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>攻击+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>ChoiceOption</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>护甲+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Hp</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>ChoiceOption</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>血量上限与当前血量+2</t>
         </is>
       </c>
     </row>
